--- a/data/commodity/Lithium.xlsx
+++ b/data/commodity/Lithium.xlsx
@@ -1,16 +1,16 @@
 
 <file path=xl/workbook.xml><?xml version="1.0" encoding="utf-8"?>
 <workbook xmlns="http://schemas.openxmlformats.org/spreadsheetml/2006/main" xmlns:r="http://schemas.openxmlformats.org/officeDocument/2006/relationships" xmlns:mc="http://schemas.openxmlformats.org/markup-compatibility/2006" xmlns:x15="http://schemas.microsoft.com/office/spreadsheetml/2010/11/main" xmlns:xr="http://schemas.microsoft.com/office/spreadsheetml/2014/revision" xmlns:xr6="http://schemas.microsoft.com/office/spreadsheetml/2016/revision6" xmlns:xr10="http://schemas.microsoft.com/office/spreadsheetml/2016/revision10" xmlns:xr2="http://schemas.microsoft.com/office/spreadsheetml/2015/revision2" mc:Ignorable="x15 xr xr6 xr10 xr2">
-  <fileVersion appName="xl" lastEdited="7" lowestEdited="6" rupBuild="20417"/>
+  <fileVersion appName="xl" lastEdited="7" lowestEdited="6" rupBuild="24334"/>
   <workbookPr/>
   <mc:AlternateContent xmlns:mc="http://schemas.openxmlformats.org/markup-compatibility/2006">
     <mc:Choice Requires="x15">
-      <x15ac:absPath xmlns:x15ac="http://schemas.microsoft.com/office/spreadsheetml/2010/11/ac" url="C:\Users\USER\PycharmProjects\AlternativeData\data\commodity\"/>
+      <x15ac:absPath xmlns:x15ac="http://schemas.microsoft.com/office/spreadsheetml/2010/11/ac" url="C:\Users\krm12\PycharmProjects\AlternativeData\data\commodity\"/>
     </mc:Choice>
   </mc:AlternateContent>
-  <xr:revisionPtr revIDLastSave="0" documentId="13_ncr:1_{2E8EF842-96BA-47EE-994A-55ADACB5E13F}" xr6:coauthVersionLast="36" xr6:coauthVersionMax="47" xr10:uidLastSave="{00000000-0000-0000-0000-000000000000}"/>
+  <xr:revisionPtr revIDLastSave="0" documentId="13_ncr:1_{53EBC608-6B26-43A0-91F2-B1A925DF2037}" xr6:coauthVersionLast="47" xr6:coauthVersionMax="47" xr10:uidLastSave="{00000000-0000-0000-0000-000000000000}"/>
   <bookViews>
-    <workbookView xWindow="27900" yWindow="1545" windowWidth="18015" windowHeight="20685" xr2:uid="{00000000-000D-0000-FFFF-FFFF00000000}"/>
+    <workbookView xWindow="28680" yWindow="-5790" windowWidth="29040" windowHeight="15720" activeTab="2" xr2:uid="{00000000-000D-0000-FFFF-FFFF00000000}"/>
   </bookViews>
   <sheets>
     <sheet name="Lithium" sheetId="1" r:id="rId1"/>
@@ -22,12 +22,24 @@
     <ext xmlns:x15="http://schemas.microsoft.com/office/spreadsheetml/2010/11/main" uri="{140A7094-0E35-4892-8432-C4D2E57EDEB5}">
       <x15:workbookPr chartTrackingRefBase="1"/>
     </ext>
+    <ext xmlns:xcalcf="http://schemas.microsoft.com/office/spreadsheetml/2018/calcfeatures" uri="{B58B0392-4F1F-4190-BB64-5DF3571DCE5F}">
+      <xcalcf:calcFeatures>
+        <xcalcf:feature name="microsoft.com:RD"/>
+        <xcalcf:feature name="microsoft.com:Single"/>
+        <xcalcf:feature name="microsoft.com:FV"/>
+        <xcalcf:feature name="microsoft.com:CNMTM"/>
+        <xcalcf:feature name="microsoft.com:LET_WF"/>
+      </xcalcf:calcFeatures>
+    </ext>
+    <ext xmlns:xlwcv="http://schemas.microsoft.com/office/spreadsheetml/2024/workbookCompatibilityVersion" uri="{D14903EA-33C4-47F7-8F05-3474C54BE107}">
+      <xlwcv:version setVersion="1"/>
+    </ext>
   </extLst>
 </workbook>
 </file>
 
 <file path=xl/sharedStrings.xml><?xml version="1.0" encoding="utf-8"?>
-<sst xmlns="http://schemas.openxmlformats.org/spreadsheetml/2006/main" count="2222" uniqueCount="16">
+<sst xmlns="http://schemas.openxmlformats.org/spreadsheetml/2006/main" count="2236" uniqueCount="16">
   <si>
     <t>source</t>
     <phoneticPr fontId="2" type="noConversion"/>
@@ -289,10 +301,10 @@
           </c:marker>
           <c:cat>
             <c:numRef>
-              <c:f>Lithium!$B$2:$B$12177</c:f>
+              <c:f>Lithium!$B$2:$B$12170</c:f>
               <c:numCache>
                 <c:formatCode>yyyy\-mm\-dd;@</c:formatCode>
-                <c:ptCount val="12176"/>
+                <c:ptCount val="12169"/>
                 <c:pt idx="0">
                   <c:v>42865</c:v>
                 </c:pt>
@@ -6916,16 +6928,58 @@
                 </c:pt>
                 <c:pt idx="2207">
                   <c:v>46098</c:v>
+                </c:pt>
+                <c:pt idx="2208">
+                  <c:v>46099</c:v>
+                </c:pt>
+                <c:pt idx="2209">
+                  <c:v>46100</c:v>
+                </c:pt>
+                <c:pt idx="2210">
+                  <c:v>46101</c:v>
+                </c:pt>
+                <c:pt idx="2211">
+                  <c:v>46104</c:v>
+                </c:pt>
+                <c:pt idx="2212">
+                  <c:v>46105</c:v>
+                </c:pt>
+                <c:pt idx="2213">
+                  <c:v>46106</c:v>
+                </c:pt>
+                <c:pt idx="2214">
+                  <c:v>46107</c:v>
+                </c:pt>
+                <c:pt idx="2215">
+                  <c:v>46108</c:v>
+                </c:pt>
+                <c:pt idx="2216">
+                  <c:v>46111</c:v>
+                </c:pt>
+                <c:pt idx="2217">
+                  <c:v>46112</c:v>
+                </c:pt>
+                <c:pt idx="2218">
+                  <c:v>46113</c:v>
+                </c:pt>
+                <c:pt idx="2219">
+                  <c:v>46114</c:v>
+                </c:pt>
+                <c:pt idx="2220">
+                  <c:v>46115</c:v>
+                </c:pt>
+                <c:pt idx="2221">
+                  <c:v>46119</c:v>
                 </c:pt>
               </c:numCache>
             </c:numRef>
           </c:cat>
           <c:val>
             <c:numRef>
-              <c:f>Lithium!$H$2:$H$12177</c:f>
+              <c:f>Lithium!$H$2:$H$12170</c:f>
               <c:numCache>
                 <c:formatCode>_(* #,##0_);_(* \(#,##0\);_(* "-"??_);_(@_)</c:formatCode>
-                <c:ptCount val="12176"/>
+                <c:ptCount val="12169"/>
                 <c:pt idx="0">
                   <c:v>136000</c:v>
                 </c:pt>
@@ -13549,6 +13603,48 @@
                 </c:pt>
                 <c:pt idx="2207">
                   <c:v>158000</c:v>
+                </c:pt>
+                <c:pt idx="2208">
+                  <c:v>155500</c:v>
+                </c:pt>
+                <c:pt idx="2209">
+                  <c:v>152500</c:v>
+                </c:pt>
+                <c:pt idx="2210">
+                  <c:v>149000</c:v>
+                </c:pt>
+                <c:pt idx="2211">
+                  <c:v>146500</c:v>
+                </c:pt>
+                <c:pt idx="2212">
+                  <c:v>147500</c:v>
+                </c:pt>
+                <c:pt idx="2213">
+                  <c:v>152500</c:v>
+                </c:pt>
+                <c:pt idx="2214">
+                  <c:v>156500</c:v>
+                </c:pt>
+                <c:pt idx="2215">
+                  <c:v>158000</c:v>
+                </c:pt>
+                <c:pt idx="2216">
+                  <c:v>164500</c:v>
+                </c:pt>
+                <c:pt idx="2217">
+                  <c:v>163000</c:v>
+                </c:pt>
+                <c:pt idx="2218">
+                  <c:v>161500</c:v>
+                </c:pt>
+                <c:pt idx="2219">
+                  <c:v>159500</c:v>
+                </c:pt>
+                <c:pt idx="2220">
+                  <c:v>158500</c:v>
+                </c:pt>
+                <c:pt idx="2221">
+                  <c:v>159000</c:v>
                 </c:pt>
               </c:numCache>
             </c:numRef>
@@ -13610,8 +13706,8 @@
                     <a:lumOff val="35000"/>
                   </a:schemeClr>
                 </a:solidFill>
-                <a:latin typeface="+mn-lt"/>
-                <a:ea typeface="+mn-ea"/>
+                <a:latin typeface="Verdana" panose="020B0604030504040204" pitchFamily="34" charset="0"/>
+                <a:ea typeface="Verdana" panose="020B0604030504040204" pitchFamily="34" charset="0"/>
                 <a:cs typeface="+mn-cs"/>
               </a:defRPr>
             </a:pPr>
@@ -13668,8 +13764,8 @@
                     <a:lumOff val="35000"/>
                   </a:schemeClr>
                 </a:solidFill>
-                <a:latin typeface="+mn-lt"/>
-                <a:ea typeface="+mn-ea"/>
+                <a:latin typeface="Verdana" panose="020B0604030504040204" pitchFamily="34" charset="0"/>
+                <a:ea typeface="Verdana" panose="020B0604030504040204" pitchFamily="34" charset="0"/>
                 <a:cs typeface="+mn-cs"/>
               </a:defRPr>
             </a:pPr>
@@ -13710,8 +13806,8 @@
                   <a:lumOff val="35000"/>
                 </a:schemeClr>
               </a:solidFill>
-              <a:latin typeface="+mn-lt"/>
-              <a:ea typeface="+mn-ea"/>
+              <a:latin typeface="Verdana" panose="020B0604030504040204" pitchFamily="34" charset="0"/>
+              <a:ea typeface="Verdana" panose="020B0604030504040204" pitchFamily="34" charset="0"/>
               <a:cs typeface="+mn-cs"/>
             </a:defRPr>
           </a:pPr>
@@ -13745,7 +13841,10 @@
     <a:lstStyle/>
     <a:p>
       <a:pPr>
-        <a:defRPr/>
+        <a:defRPr>
+          <a:latin typeface="Verdana" panose="020B0604030504040204" pitchFamily="34" charset="0"/>
+          <a:ea typeface="Verdana" panose="020B0604030504040204" pitchFamily="34" charset="0"/>
+        </a:defRPr>
       </a:pPr>
       <a:endParaRPr lang="ko-KR"/>
     </a:p>
@@ -14620,7 +14719,7 @@
 
 <file path=xl/worksheets/sheet1.xml><?xml version="1.0" encoding="utf-8"?>
 <worksheet xmlns="http://schemas.openxmlformats.org/spreadsheetml/2006/main" xmlns:r="http://schemas.openxmlformats.org/officeDocument/2006/relationships" xmlns:mc="http://schemas.openxmlformats.org/markup-compatibility/2006" xmlns:x14ac="http://schemas.microsoft.com/office/spreadsheetml/2009/9/ac" xmlns:xr="http://schemas.microsoft.com/office/spreadsheetml/2014/revision" xmlns:xr2="http://schemas.microsoft.com/office/spreadsheetml/2015/revision2" xmlns:xr3="http://schemas.microsoft.com/office/spreadsheetml/2016/revision3" mc:Ignorable="x14ac xr xr2 xr3" xr:uid="{00000000-0001-0000-0000-000000000000}">
-  <dimension ref="A1:H2209"/>
+  <dimension ref="A1:H2223"/>
   <sheetFormatPr defaultColWidth="9" defaultRowHeight="12.75" x14ac:dyDescent="0.2"/>
   <cols>
     <col min="1" max="1" width="12.125" style="3" bestFit="1" customWidth="1"/>
@@ -59374,6 +59473,370 @@
       </c>
       <c r="H2209" s="10">
         <v>158000</v>
+      </c>
+    </row>
+    <row r="2210" spans="1:8" x14ac:dyDescent="0.2">
+      <c r="A2210" s="3">
+        <v>46099</v>
+      </c>
+      <c r="B2210" s="3">
+        <v>46099</v>
+      </c>
+      <c r="C2210" s="19">
+        <v>0.625</v>
+      </c>
+      <c r="D2210" s="4" t="s">
+        <v>10</v>
+      </c>
+      <c r="E2210" s="16">
+        <v>155500</v>
+      </c>
+      <c r="F2210" s="16">
+        <v>160000</v>
+      </c>
+      <c r="G2210" s="16">
+        <v>151000</v>
+      </c>
+      <c r="H2210" s="10">
+        <v>155500</v>
+      </c>
+    </row>
+    <row r="2211" spans="1:8" x14ac:dyDescent="0.2">
+      <c r="A2211" s="3">
+        <v>46100</v>
+      </c>
+      <c r="B2211" s="3">
+        <v>46100</v>
+      </c>
+      <c r="C2211" s="19">
+        <v>0.625</v>
+      </c>
+      <c r="D2211" s="4" t="s">
+        <v>10</v>
+      </c>
+      <c r="E2211" s="16">
+        <v>152500</v>
+      </c>
+      <c r="F2211" s="16">
+        <v>158000</v>
+      </c>
+      <c r="G2211" s="16">
+        <v>147000</v>
+      </c>
+      <c r="H2211" s="10">
+        <v>152500</v>
+      </c>
+    </row>
+    <row r="2212" spans="1:8" x14ac:dyDescent="0.2">
+      <c r="A2212" s="3">
+        <v>46101</v>
+      </c>
+      <c r="B2212" s="3">
+        <v>46101</v>
+      </c>
+      <c r="C2212" s="19">
+        <v>0.625</v>
+      </c>
+      <c r="D2212" s="4" t="s">
+        <v>10</v>
+      </c>
+      <c r="E2212" s="16">
+        <v>149000</v>
+      </c>
+      <c r="F2212" s="16">
+        <v>156000</v>
+      </c>
+      <c r="G2212" s="16">
+        <v>142000</v>
+      </c>
+      <c r="H2212" s="10">
+        <v>149000</v>
+      </c>
+    </row>
+    <row r="2213" spans="1:8" x14ac:dyDescent="0.2">
+      <c r="A2213" s="3">
+        <v>46104</v>
+      </c>
+      <c r="B2213" s="3">
+        <v>46104</v>
+      </c>
+      <c r="C2213" s="19">
+        <v>0.625</v>
+      </c>
+      <c r="D2213" s="4" t="s">
+        <v>10</v>
+      </c>
+      <c r="E2213" s="16">
+        <v>146500</v>
+      </c>
+      <c r="F2213" s="16">
+        <v>151000</v>
+      </c>
+      <c r="G2213" s="16">
+        <v>142000</v>
+      </c>
+      <c r="H2213" s="10">
+        <v>146500</v>
+      </c>
+    </row>
+    <row r="2214" spans="1:8" x14ac:dyDescent="0.2">
+      <c r="A2214" s="3">
+        <v>46105</v>
+      </c>
+      <c r="B2214" s="3">
+        <v>46105</v>
+      </c>
+      <c r="C2214" s="19">
+        <v>0.625</v>
+      </c>
+      <c r="D2214" s="4" t="s">
+        <v>10</v>
+      </c>
+      <c r="E2214" s="16">
+        <v>147500</v>
+      </c>
+      <c r="F2214" s="16">
+        <v>154000</v>
+      </c>
+      <c r="G2214" s="16">
+        <v>141000</v>
+      </c>
+      <c r="H2214" s="10">
+        <v>147500</v>
+      </c>
+    </row>
+    <row r="2215" spans="1:8" x14ac:dyDescent="0.2">
+      <c r="A2215" s="3">
+        <v>46106</v>
+      </c>
+      <c r="B2215" s="3">
+        <v>46106</v>
+      </c>
+      <c r="C2215" s="19">
+        <v>0.625</v>
+      </c>
+      <c r="D2215" s="4" t="s">
+        <v>10</v>
+      </c>
+      <c r="E2215" s="16">
+        <v>152500</v>
+      </c>
+      <c r="F2215" s="16">
+        <v>158000</v>
+      </c>
+      <c r="G2215" s="16">
+        <v>147000</v>
+      </c>
+      <c r="H2215" s="10">
+        <v>152500</v>
+      </c>
+    </row>
+    <row r="2216" spans="1:8" x14ac:dyDescent="0.2">
+      <c r="A2216" s="3">
+        <v>46107</v>
+      </c>
+      <c r="B2216" s="3">
+        <v>46107</v>
+      </c>
+      <c r="C2216" s="19">
+        <v>0.625</v>
+      </c>
+      <c r="D2216" s="4" t="s">
+        <v>10</v>
+      </c>
+      <c r="E2216" s="16">
+        <v>156500</v>
+      </c>
+      <c r="F2216" s="16">
+        <v>162000</v>
+      </c>
+      <c r="G2216" s="16">
+        <v>151000</v>
+      </c>
+      <c r="H2216" s="10">
+        <v>156500</v>
+      </c>
+    </row>
+    <row r="2217" spans="1:8" x14ac:dyDescent="0.2">
+      <c r="A2217" s="3">
+        <v>46108</v>
+      </c>
+      <c r="B2217" s="3">
+        <v>46108</v>
+      </c>
+      <c r="C2217" s="19">
+        <v>0.625</v>
+      </c>
+      <c r="D2217" s="4" t="s">
+        <v>10</v>
+      </c>
+      <c r="E2217" s="16">
+        <v>158000</v>
+      </c>
+      <c r="F2217" s="16">
+        <v>161000</v>
+      </c>
+      <c r="G2217" s="16">
+        <v>155000</v>
+      </c>
+      <c r="H2217" s="10">
+        <v>158000</v>
+      </c>
+    </row>
+    <row r="2218" spans="1:8" x14ac:dyDescent="0.2">
+      <c r="A2218" s="3">
+        <v>46111</v>
+      </c>
+      <c r="B2218" s="3">
+        <v>46111</v>
+      </c>
+      <c r="C2218" s="19">
+        <v>0.625</v>
+      </c>
+      <c r="D2218" s="4" t="s">
+        <v>10</v>
+      </c>
+      <c r="E2218" s="16">
+        <v>164500</v>
+      </c>
+      <c r="F2218" s="16">
+        <v>169000</v>
+      </c>
+      <c r="G2218" s="16">
+        <v>157968</v>
+      </c>
+      <c r="H2218" s="10">
+        <v>164500</v>
+      </c>
+    </row>
+    <row r="2219" spans="1:8" x14ac:dyDescent="0.2">
+      <c r="A2219" s="3">
+        <v>46112</v>
+      </c>
+      <c r="B2219" s="3">
+        <v>46112</v>
+      </c>
+      <c r="C2219" s="19">
+        <v>0.625</v>
+      </c>
+      <c r="D2219" s="4" t="s">
+        <v>10</v>
+      </c>
+      <c r="E2219" s="16">
+        <v>163000</v>
+      </c>
+      <c r="F2219" s="16">
+        <v>166000</v>
+      </c>
+      <c r="G2219" s="16">
+        <v>160000</v>
+      </c>
+      <c r="H2219" s="10">
+        <v>163000</v>
+      </c>
+    </row>
+    <row r="2220" spans="1:8" x14ac:dyDescent="0.2">
+      <c r="A2220" s="3">
+        <v>46113</v>
+      </c>
+      <c r="B2220" s="3">
+        <v>46113</v>
+      </c>
+      <c r="C2220" s="19">
+        <v>0.625</v>
+      </c>
+      <c r="D2220" s="4" t="s">
+        <v>10</v>
+      </c>
+      <c r="E2220" s="16">
+        <v>161500</v>
+      </c>
+      <c r="F2220" s="16">
+        <v>165000</v>
+      </c>
+      <c r="G2220" s="16">
+        <v>158000</v>
+      </c>
+      <c r="H2220" s="10">
+        <v>161500</v>
+      </c>
+    </row>
+    <row r="2221" spans="1:8" x14ac:dyDescent="0.2">
+      <c r="A2221" s="3">
+        <v>46114</v>
+      </c>
+      <c r="B2221" s="3">
+        <v>46114</v>
+      </c>
+      <c r="C2221" s="19">
+        <v>0.625</v>
+      </c>
+      <c r="D2221" s="4" t="s">
+        <v>10</v>
+      </c>
+      <c r="E2221" s="16">
+        <v>159500</v>
+      </c>
+      <c r="F2221" s="16">
+        <v>164000</v>
+      </c>
+      <c r="G2221" s="16">
+        <v>155000</v>
+      </c>
+      <c r="H2221" s="10">
+        <v>159500</v>
+      </c>
+    </row>
+    <row r="2222" spans="1:8" x14ac:dyDescent="0.2">
+      <c r="A2222" s="3">
+        <v>46115</v>
+      </c>
+      <c r="B2222" s="3">
+        <v>46115</v>
+      </c>
+      <c r="C2222" s="19">
+        <v>0.625</v>
+      </c>
+      <c r="D2222" s="4" t="s">
+        <v>10</v>
+      </c>
+      <c r="E2222" s="16">
+        <v>158500</v>
+      </c>
+      <c r="F2222" s="16">
+        <v>161000</v>
+      </c>
+      <c r="G2222" s="16">
+        <v>156000</v>
+      </c>
+      <c r="H2222" s="10">
+        <v>158500</v>
+      </c>
+    </row>
+    <row r="2223" spans="1:8" x14ac:dyDescent="0.2">
+      <c r="A2223" s="3">
+        <v>46119</v>
+      </c>
+      <c r="B2223" s="3">
+        <v>46119</v>
+      </c>
+      <c r="C2223" s="19">
+        <v>0.625</v>
+      </c>
+      <c r="D2223" s="4" t="s">
+        <v>10</v>
+      </c>
+      <c r="E2223" s="16">
+        <v>161000</v>
+      </c>
+      <c r="F2223" s="16">
+        <v>161000</v>
+      </c>
+      <c r="G2223" s="16">
+        <v>157000</v>
+      </c>
+      <c r="H2223" s="10">
+        <v>159000</v>
       </c>
     </row>
   </sheetData>

--- a/data/commodity/Lithium.xlsx
+++ b/data/commodity/Lithium.xlsx
@@ -8,7 +8,7 @@
       <x15ac:absPath xmlns:x15ac="http://schemas.microsoft.com/office/spreadsheetml/2010/11/ac" url="C:\Users\krm\PycharmProjects\AlternativeData\data\commodity\"/>
     </mc:Choice>
   </mc:AlternateContent>
-  <xr:revisionPtr revIDLastSave="0" documentId="13_ncr:1_{290BB679-305F-4A2D-85B0-D7B7E5C26FC9}" xr6:coauthVersionLast="47" xr6:coauthVersionMax="47" xr10:uidLastSave="{00000000-0000-0000-0000-000000000000}"/>
+  <xr:revisionPtr revIDLastSave="0" documentId="13_ncr:1_{04EB4AD4-FB85-417D-B303-A5F00516E89E}" xr6:coauthVersionLast="47" xr6:coauthVersionMax="47" xr10:uidLastSave="{00000000-0000-0000-0000-000000000000}"/>
   <bookViews>
     <workbookView xWindow="28680" yWindow="-120" windowWidth="29040" windowHeight="15720" xr2:uid="{00000000-000D-0000-FFFF-FFFF00000000}"/>
   </bookViews>
@@ -36,7 +36,7 @@
 </file>
 
 <file path=xl/sharedStrings.xml><?xml version="1.0" encoding="utf-8"?>
-<sst xmlns="http://schemas.openxmlformats.org/spreadsheetml/2006/main" count="2240" uniqueCount="16">
+<sst xmlns="http://schemas.openxmlformats.org/spreadsheetml/2006/main" count="2241" uniqueCount="16">
   <si>
     <t>source</t>
     <phoneticPr fontId="2" type="noConversion"/>
@@ -6980,6 +6980,9 @@
                 <c:pt idx="2225">
                   <c:v>46125</c:v>
                 </c:pt>
+                <c:pt idx="2226">
+                  <c:v>46126</c:v>
+                </c:pt>
               </c:numCache>
             </c:numRef>
           </c:cat>
@@ -13666,6 +13669,9 @@
                 </c:pt>
                 <c:pt idx="2225">
                   <c:v>157000</c:v>
+                </c:pt>
+                <c:pt idx="2226">
+                  <c:v>161500</c:v>
                 </c:pt>
               </c:numCache>
             </c:numRef>
@@ -14740,7 +14746,7 @@
 
 <file path=xl/worksheets/sheet1.xml><?xml version="1.0" encoding="utf-8"?>
 <worksheet xmlns="http://schemas.openxmlformats.org/spreadsheetml/2006/main" xmlns:r="http://schemas.openxmlformats.org/officeDocument/2006/relationships" xmlns:mc="http://schemas.openxmlformats.org/markup-compatibility/2006" xmlns:x14ac="http://schemas.microsoft.com/office/spreadsheetml/2009/9/ac" xmlns:xr="http://schemas.microsoft.com/office/spreadsheetml/2014/revision" xmlns:xr2="http://schemas.microsoft.com/office/spreadsheetml/2015/revision2" xmlns:xr3="http://schemas.microsoft.com/office/spreadsheetml/2016/revision3" mc:Ignorable="x14ac xr xr2 xr3" xr:uid="{00000000-0001-0000-0000-000000000000}">
-  <dimension ref="A1:H2227"/>
+  <dimension ref="A1:H2228"/>
   <sheetFormatPr defaultColWidth="9" defaultRowHeight="12.6" x14ac:dyDescent="0.2"/>
   <cols>
     <col min="1" max="1" width="12.09765625" style="3" bestFit="1" customWidth="1"/>
@@ -59962,6 +59968,32 @@
       </c>
       <c r="H2227" s="10">
         <v>157000</v>
+      </c>
+    </row>
+    <row r="2228" spans="1:8" x14ac:dyDescent="0.2">
+      <c r="A2228" s="3">
+        <v>46126</v>
+      </c>
+      <c r="B2228" s="9">
+        <v>46126</v>
+      </c>
+      <c r="C2228" s="19">
+        <v>0.625</v>
+      </c>
+      <c r="D2228" s="4" t="s">
+        <v>10</v>
+      </c>
+      <c r="E2228" s="16">
+        <v>156984</v>
+      </c>
+      <c r="F2228" s="16">
+        <v>163000</v>
+      </c>
+      <c r="G2228" s="16">
+        <v>156969</v>
+      </c>
+      <c r="H2228" s="10">
+        <v>161500</v>
       </c>
     </row>
   </sheetData>

--- a/data/commodity/Lithium.xlsx
+++ b/data/commodity/Lithium.xlsx
@@ -8,7 +8,7 @@
       <x15ac:absPath xmlns:x15ac="http://schemas.microsoft.com/office/spreadsheetml/2010/11/ac" url="C:\Users\krm\PycharmProjects\AlternativeData\data\commodity\"/>
     </mc:Choice>
   </mc:AlternateContent>
-  <xr:revisionPtr revIDLastSave="0" documentId="13_ncr:1_{02AA49C2-0A23-4BB4-A726-2841FDCF35BF}" xr6:coauthVersionLast="47" xr6:coauthVersionMax="47" xr10:uidLastSave="{00000000-0000-0000-0000-000000000000}"/>
+  <xr:revisionPtr revIDLastSave="0" documentId="13_ncr:1_{1613EF62-6DB9-47DF-8EDD-F5FB9DA932E9}" xr6:coauthVersionLast="47" xr6:coauthVersionMax="47" xr10:uidLastSave="{00000000-0000-0000-0000-000000000000}"/>
   <bookViews>
     <workbookView xWindow="28680" yWindow="-120" windowWidth="29040" windowHeight="15720" xr2:uid="{00000000-000D-0000-FFFF-FFFF00000000}"/>
   </bookViews>
@@ -36,7 +36,7 @@
 </file>
 
 <file path=xl/sharedStrings.xml><?xml version="1.0" encoding="utf-8"?>
-<sst xmlns="http://schemas.openxmlformats.org/spreadsheetml/2006/main" count="2242" uniqueCount="16">
+<sst xmlns="http://schemas.openxmlformats.org/spreadsheetml/2006/main" count="2243" uniqueCount="16">
   <si>
     <t>source</t>
     <phoneticPr fontId="2" type="noConversion"/>
@@ -6986,6 +6986,9 @@
                 <c:pt idx="2227">
                   <c:v>46127</c:v>
                 </c:pt>
+                <c:pt idx="2228">
+                  <c:v>46128</c:v>
+                </c:pt>
               </c:numCache>
             </c:numRef>
           </c:cat>
@@ -13678,6 +13681,9 @@
                 </c:pt>
                 <c:pt idx="2227">
                   <c:v>166000</c:v>
+                </c:pt>
+                <c:pt idx="2228">
+                  <c:v>167500</c:v>
                 </c:pt>
               </c:numCache>
             </c:numRef>
@@ -14752,7 +14758,7 @@
 
 <file path=xl/worksheets/sheet1.xml><?xml version="1.0" encoding="utf-8"?>
 <worksheet xmlns="http://schemas.openxmlformats.org/spreadsheetml/2006/main" xmlns:r="http://schemas.openxmlformats.org/officeDocument/2006/relationships" xmlns:mc="http://schemas.openxmlformats.org/markup-compatibility/2006" xmlns:x14ac="http://schemas.microsoft.com/office/spreadsheetml/2009/9/ac" xmlns:xr="http://schemas.microsoft.com/office/spreadsheetml/2014/revision" xmlns:xr2="http://schemas.microsoft.com/office/spreadsheetml/2015/revision2" xmlns:xr3="http://schemas.microsoft.com/office/spreadsheetml/2016/revision3" mc:Ignorable="x14ac xr xr2 xr3" xr:uid="{00000000-0001-0000-0000-000000000000}">
-  <dimension ref="A1:H2229"/>
+  <dimension ref="A1:H2230"/>
   <sheetFormatPr defaultColWidth="9" defaultRowHeight="12.6" x14ac:dyDescent="0.2"/>
   <cols>
     <col min="1" max="1" width="12.09765625" style="3" bestFit="1" customWidth="1"/>
@@ -60026,6 +60032,32 @@
       </c>
       <c r="H2229" s="10">
         <v>166000</v>
+      </c>
+    </row>
+    <row r="2230" spans="1:8" x14ac:dyDescent="0.2">
+      <c r="A2230" s="3">
+        <v>46128</v>
+      </c>
+      <c r="B2230" s="3">
+        <v>46128</v>
+      </c>
+      <c r="C2230" s="19">
+        <v>0.625</v>
+      </c>
+      <c r="D2230" s="4" t="s">
+        <v>10</v>
+      </c>
+      <c r="E2230" s="16">
+        <v>167500</v>
+      </c>
+      <c r="F2230" s="16">
+        <v>170000</v>
+      </c>
+      <c r="G2230" s="16">
+        <v>165000</v>
+      </c>
+      <c r="H2230" s="10">
+        <v>167500</v>
       </c>
     </row>
   </sheetData>

--- a/data/commodity/Lithium.xlsx
+++ b/data/commodity/Lithium.xlsx
@@ -8,9 +8,9 @@
       <x15ac:absPath xmlns:x15ac="http://schemas.microsoft.com/office/spreadsheetml/2010/11/ac" url="C:\Users\krm\PycharmProjects\AlternativeData\data\commodity\"/>
     </mc:Choice>
   </mc:AlternateContent>
-  <xr:revisionPtr revIDLastSave="0" documentId="13_ncr:1_{2FD86C80-3DFB-4295-98F2-867BE0B583EC}" xr6:coauthVersionLast="47" xr6:coauthVersionMax="47" xr10:uidLastSave="{00000000-0000-0000-0000-000000000000}"/>
+  <xr:revisionPtr revIDLastSave="0" documentId="13_ncr:1_{6DC59AAE-896C-400A-9DC9-E18484D61A33}" xr6:coauthVersionLast="47" xr6:coauthVersionMax="47" xr10:uidLastSave="{00000000-0000-0000-0000-000000000000}"/>
   <bookViews>
-    <workbookView xWindow="28680" yWindow="-120" windowWidth="29040" windowHeight="15720" xr2:uid="{00000000-000D-0000-FFFF-FFFF00000000}"/>
+    <workbookView xWindow="28680" yWindow="-120" windowWidth="29040" windowHeight="15720" activeTab="2" xr2:uid="{00000000-000D-0000-FFFF-FFFF00000000}"/>
   </bookViews>
   <sheets>
     <sheet name="Lithium" sheetId="1" r:id="rId1"/>
@@ -36,7 +36,7 @@
 </file>
 
 <file path=xl/sharedStrings.xml><?xml version="1.0" encoding="utf-8"?>
-<sst xmlns="http://schemas.openxmlformats.org/spreadsheetml/2006/main" count="2264" uniqueCount="16">
+<sst xmlns="http://schemas.openxmlformats.org/spreadsheetml/2006/main" count="2265" uniqueCount="16">
   <si>
     <t>source</t>
     <phoneticPr fontId="2" type="noConversion"/>
@@ -7052,6 +7052,9 @@
                 <c:pt idx="2249">
                   <c:v>46162</c:v>
                 </c:pt>
+                <c:pt idx="2250">
+                  <c:v>46163</c:v>
+                </c:pt>
               </c:numCache>
             </c:numRef>
           </c:cat>
@@ -13810,6 +13813,9 @@
                 </c:pt>
                 <c:pt idx="2249">
                   <c:v>179000</c:v>
+                </c:pt>
+                <c:pt idx="2250">
+                  <c:v>182000</c:v>
                 </c:pt>
               </c:numCache>
             </c:numRef>
@@ -14889,7 +14895,7 @@
 
 <file path=xl/worksheets/sheet1.xml><?xml version="1.0" encoding="utf-8"?>
 <worksheet xmlns="http://schemas.openxmlformats.org/spreadsheetml/2006/main" xmlns:r="http://schemas.openxmlformats.org/officeDocument/2006/relationships" xmlns:mc="http://schemas.openxmlformats.org/markup-compatibility/2006" xmlns:x14ac="http://schemas.microsoft.com/office/spreadsheetml/2009/9/ac" xmlns:xr="http://schemas.microsoft.com/office/spreadsheetml/2014/revision" xmlns:xr2="http://schemas.microsoft.com/office/spreadsheetml/2015/revision2" xmlns:xr3="http://schemas.microsoft.com/office/spreadsheetml/2016/revision3" mc:Ignorable="x14ac xr xr2 xr3" xr:uid="{00000000-0001-0000-0000-000000000000}">
-  <dimension ref="A1:H2251"/>
+  <dimension ref="A1:H2252"/>
   <sheetFormatPr defaultColWidth="9" defaultRowHeight="12.6"/>
   <cols>
     <col min="1" max="1" width="12.5546875" style="3" bestFit="1" customWidth="1"/>
@@ -60735,6 +60741,32 @@
       </c>
       <c r="H2251" s="10">
         <v>179000</v>
+      </c>
+    </row>
+    <row r="2252" spans="1:8">
+      <c r="A2252" s="3">
+        <v>46163</v>
+      </c>
+      <c r="B2252" s="3">
+        <v>46163</v>
+      </c>
+      <c r="C2252" s="19">
+        <v>0.625</v>
+      </c>
+      <c r="D2252" s="4" t="s">
+        <v>10</v>
+      </c>
+      <c r="E2252" s="16">
+        <v>179036</v>
+      </c>
+      <c r="F2252" s="16">
+        <v>184000</v>
+      </c>
+      <c r="G2252" s="16">
+        <v>178964</v>
+      </c>
+      <c r="H2252" s="10">
+        <v>182000</v>
       </c>
     </row>
   </sheetData>

--- a/data/commodity/Lithium.xlsx
+++ b/data/commodity/Lithium.xlsx
@@ -1,16 +1,16 @@
 
 <file path=xl/workbook.xml><?xml version="1.0" encoding="utf-8"?>
 <workbook xmlns="http://schemas.openxmlformats.org/spreadsheetml/2006/main" xmlns:r="http://schemas.openxmlformats.org/officeDocument/2006/relationships" xmlns:mc="http://schemas.openxmlformats.org/markup-compatibility/2006" xmlns:x15="http://schemas.microsoft.com/office/spreadsheetml/2010/11/main" xmlns:xr="http://schemas.microsoft.com/office/spreadsheetml/2014/revision" xmlns:xr6="http://schemas.microsoft.com/office/spreadsheetml/2016/revision6" xmlns:xr10="http://schemas.microsoft.com/office/spreadsheetml/2016/revision10" xmlns:xr2="http://schemas.microsoft.com/office/spreadsheetml/2015/revision2" mc:Ignorable="x15 xr xr6 xr10 xr2">
-  <fileVersion appName="xl" lastEdited="7" lowestEdited="6" rupBuild="29929"/>
+  <fileVersion appName="xl" lastEdited="7" lowestEdited="6" rupBuild="30026"/>
   <workbookPr/>
   <mc:AlternateContent xmlns:mc="http://schemas.openxmlformats.org/markup-compatibility/2006">
     <mc:Choice Requires="x15">
-      <x15ac:absPath xmlns:x15ac="http://schemas.microsoft.com/office/spreadsheetml/2010/11/ac" url="C:\Users\krm\PycharmProjects\AlternativeData\data\commodity\"/>
+      <x15ac:absPath xmlns:x15ac="http://schemas.microsoft.com/office/spreadsheetml/2010/11/ac" url="C:\Users\Geust\PycharmProjects\AlternativeData\data\commodity\"/>
     </mc:Choice>
   </mc:AlternateContent>
-  <xr:revisionPtr revIDLastSave="0" documentId="13_ncr:1_{6DC59AAE-896C-400A-9DC9-E18484D61A33}" xr6:coauthVersionLast="47" xr6:coauthVersionMax="47" xr10:uidLastSave="{00000000-0000-0000-0000-000000000000}"/>
+  <xr:revisionPtr revIDLastSave="0" documentId="13_ncr:1_{96951D5B-2FC1-48B6-AA08-A0F827D80B6E}" xr6:coauthVersionLast="47" xr6:coauthVersionMax="47" xr10:uidLastSave="{00000000-0000-0000-0000-000000000000}"/>
   <bookViews>
-    <workbookView xWindow="28680" yWindow="-120" windowWidth="29040" windowHeight="15720" activeTab="2" xr2:uid="{00000000-000D-0000-FFFF-FFFF00000000}"/>
+    <workbookView xWindow="-110" yWindow="-110" windowWidth="23260" windowHeight="14860" activeTab="2" xr2:uid="{00000000-000D-0000-FFFF-FFFF00000000}"/>
   </bookViews>
   <sheets>
     <sheet name="Lithium" sheetId="1" r:id="rId1"/>
@@ -36,7 +36,7 @@
 </file>
 
 <file path=xl/sharedStrings.xml><?xml version="1.0" encoding="utf-8"?>
-<sst xmlns="http://schemas.openxmlformats.org/spreadsheetml/2006/main" count="2265" uniqueCount="16">
+<sst xmlns="http://schemas.openxmlformats.org/spreadsheetml/2006/main" count="2266" uniqueCount="16">
   <si>
     <t>source</t>
     <phoneticPr fontId="2" type="noConversion"/>
@@ -241,9 +241,9 @@
     </xf>
   </cellXfs>
   <cellStyles count="3">
-    <cellStyle name="쉼표" xfId="1" builtinId="3"/>
-    <cellStyle name="표준" xfId="0" builtinId="0"/>
-    <cellStyle name="하이퍼링크" xfId="2" builtinId="8"/>
+    <cellStyle name="Comma" xfId="1" builtinId="3"/>
+    <cellStyle name="Hyperlink" xfId="2" builtinId="8"/>
+    <cellStyle name="Normal" xfId="0" builtinId="0"/>
   </cellStyles>
   <dxfs count="0"/>
   <tableStyles count="0" defaultTableStyle="TableStyleMedium2" defaultPivotStyle="PivotStyleLight16"/>
@@ -261,7 +261,7 @@
 <file path=xl/charts/chart1.xml><?xml version="1.0" encoding="utf-8"?>
 <c:chartSpace xmlns:c="http://schemas.openxmlformats.org/drawingml/2006/chart" xmlns:a="http://schemas.openxmlformats.org/drawingml/2006/main" xmlns:r="http://schemas.openxmlformats.org/officeDocument/2006/relationships" xmlns:c16r2="http://schemas.microsoft.com/office/drawing/2015/06/chart">
   <c:date1904 val="0"/>
-  <c:lang val="ko-KR"/>
+  <c:lang val="en-US"/>
   <c:roundedCorners val="0"/>
   <mc:AlternateContent xmlns:mc="http://schemas.openxmlformats.org/markup-compatibility/2006">
     <mc:Choice xmlns:c14="http://schemas.microsoft.com/office/drawing/2007/8/2/chart" Requires="c14">
@@ -7055,6 +7055,9 @@
                 <c:pt idx="2250">
                   <c:v>46163</c:v>
                 </c:pt>
+                <c:pt idx="2251">
+                  <c:v>46164</c:v>
+                </c:pt>
               </c:numCache>
             </c:numRef>
           </c:cat>
@@ -13816,6 +13819,9 @@
                 </c:pt>
                 <c:pt idx="2250">
                   <c:v>182000</c:v>
+                </c:pt>
+                <c:pt idx="2251">
+                  <c:v>178000</c:v>
                 </c:pt>
               </c:numCache>
             </c:numRef>
@@ -14895,15 +14901,15 @@
 
 <file path=xl/worksheets/sheet1.xml><?xml version="1.0" encoding="utf-8"?>
 <worksheet xmlns="http://schemas.openxmlformats.org/spreadsheetml/2006/main" xmlns:r="http://schemas.openxmlformats.org/officeDocument/2006/relationships" xmlns:mc="http://schemas.openxmlformats.org/markup-compatibility/2006" xmlns:x14ac="http://schemas.microsoft.com/office/spreadsheetml/2009/9/ac" xmlns:xr="http://schemas.microsoft.com/office/spreadsheetml/2014/revision" xmlns:xr2="http://schemas.microsoft.com/office/spreadsheetml/2015/revision2" xmlns:xr3="http://schemas.microsoft.com/office/spreadsheetml/2016/revision3" mc:Ignorable="x14ac xr xr2 xr3" xr:uid="{00000000-0001-0000-0000-000000000000}">
-  <dimension ref="A1:H2252"/>
-  <sheetFormatPr defaultColWidth="9" defaultRowHeight="12.6"/>
+  <dimension ref="A1:H2253"/>
+  <sheetFormatPr defaultColWidth="9" defaultRowHeight="13.5"/>
   <cols>
-    <col min="1" max="1" width="12.5546875" style="3" bestFit="1" customWidth="1"/>
-    <col min="2" max="2" width="14.109375" style="9" bestFit="1" customWidth="1"/>
-    <col min="3" max="3" width="11.5546875" style="20" customWidth="1"/>
-    <col min="4" max="4" width="11.5546875" style="11" customWidth="1"/>
-    <col min="5" max="7" width="11.5546875" style="16" customWidth="1"/>
-    <col min="8" max="8" width="10.77734375" style="10" bestFit="1" customWidth="1"/>
+    <col min="1" max="1" width="12.54296875" style="3" bestFit="1" customWidth="1"/>
+    <col min="2" max="2" width="14.08984375" style="9" bestFit="1" customWidth="1"/>
+    <col min="3" max="3" width="11.81640625" style="20" bestFit="1" customWidth="1"/>
+    <col min="4" max="4" width="11.54296875" style="11" customWidth="1"/>
+    <col min="5" max="7" width="11.54296875" style="16" customWidth="1"/>
+    <col min="8" max="8" width="10.81640625" style="10" bestFit="1" customWidth="1"/>
     <col min="9" max="16384" width="9" style="7"/>
   </cols>
   <sheetData>
@@ -60767,6 +60773,32 @@
       </c>
       <c r="H2252" s="10">
         <v>182000</v>
+      </c>
+    </row>
+    <row r="2253" spans="1:8">
+      <c r="A2253" s="3">
+        <v>46164</v>
+      </c>
+      <c r="B2253" s="9">
+        <v>46164</v>
+      </c>
+      <c r="C2253" s="19">
+        <v>0.625</v>
+      </c>
+      <c r="D2253" s="4" t="s">
+        <v>10</v>
+      </c>
+      <c r="E2253" s="16">
+        <v>182018</v>
+      </c>
+      <c r="F2253" s="16">
+        <v>182036</v>
+      </c>
+      <c r="G2253" s="16">
+        <v>176000</v>
+      </c>
+      <c r="H2253" s="10">
+        <v>178000</v>
       </c>
     </row>
   </sheetData>
@@ -60779,9 +60811,9 @@
 <file path=xl/worksheets/sheet2.xml><?xml version="1.0" encoding="utf-8"?>
 <worksheet xmlns="http://schemas.openxmlformats.org/spreadsheetml/2006/main" xmlns:r="http://schemas.openxmlformats.org/officeDocument/2006/relationships" xmlns:mc="http://schemas.openxmlformats.org/markup-compatibility/2006" xmlns:x14ac="http://schemas.microsoft.com/office/spreadsheetml/2009/9/ac" xmlns:xr="http://schemas.microsoft.com/office/spreadsheetml/2014/revision" xmlns:xr2="http://schemas.microsoft.com/office/spreadsheetml/2015/revision2" xmlns:xr3="http://schemas.microsoft.com/office/spreadsheetml/2016/revision3" mc:Ignorable="x14ac xr xr2 xr3" xr:uid="{9FF8FA39-E640-4E6A-B261-45B6002B9973}">
   <dimension ref="B2:C4"/>
-  <sheetFormatPr defaultColWidth="8.88671875" defaultRowHeight="14.4"/>
+  <sheetFormatPr defaultColWidth="8.90625" defaultRowHeight="14.5"/>
   <cols>
-    <col min="2" max="2" width="10.44140625" bestFit="1" customWidth="1"/>
+    <col min="2" max="2" width="10.453125" bestFit="1" customWidth="1"/>
   </cols>
   <sheetData>
     <row r="2" spans="2:3">
@@ -60821,7 +60853,7 @@
 <file path=xl/worksheets/sheet3.xml><?xml version="1.0" encoding="utf-8"?>
 <worksheet xmlns="http://schemas.openxmlformats.org/spreadsheetml/2006/main" xmlns:r="http://schemas.openxmlformats.org/officeDocument/2006/relationships" xmlns:mc="http://schemas.openxmlformats.org/markup-compatibility/2006" xmlns:x14ac="http://schemas.microsoft.com/office/spreadsheetml/2009/9/ac" xmlns:xr="http://schemas.microsoft.com/office/spreadsheetml/2014/revision" xmlns:xr2="http://schemas.microsoft.com/office/spreadsheetml/2015/revision2" xmlns:xr3="http://schemas.microsoft.com/office/spreadsheetml/2016/revision3" mc:Ignorable="x14ac xr xr2 xr3" xr:uid="{17A1C1D3-27CA-4F31-B658-DBB84930A46D}">
   <dimension ref="A1"/>
-  <sheetFormatPr defaultColWidth="8.88671875" defaultRowHeight="14.4"/>
+  <sheetFormatPr defaultColWidth="8.90625" defaultRowHeight="14.5"/>
   <sheetData/>
   <phoneticPr fontId="2" type="noConversion"/>
   <pageMargins left="0.7" right="0.7" top="0.75" bottom="0.75" header="0.3" footer="0.3"/>

--- a/data/commodity/Lithium.xlsx
+++ b/data/commodity/Lithium.xlsx
@@ -1,16 +1,16 @@
 
 <file path=xl/workbook.xml><?xml version="1.0" encoding="utf-8"?>
 <workbook xmlns="http://schemas.openxmlformats.org/spreadsheetml/2006/main" xmlns:r="http://schemas.openxmlformats.org/officeDocument/2006/relationships" xmlns:mc="http://schemas.openxmlformats.org/markup-compatibility/2006" xmlns:x15="http://schemas.microsoft.com/office/spreadsheetml/2010/11/main" xmlns:xr="http://schemas.microsoft.com/office/spreadsheetml/2014/revision" xmlns:xr6="http://schemas.microsoft.com/office/spreadsheetml/2016/revision6" xmlns:xr10="http://schemas.microsoft.com/office/spreadsheetml/2016/revision10" xmlns:xr2="http://schemas.microsoft.com/office/spreadsheetml/2015/revision2" mc:Ignorable="x15 xr xr6 xr10 xr2">
-  <fileVersion appName="xl" lastEdited="7" lowestEdited="6" rupBuild="30026"/>
+  <fileVersion appName="xl" lastEdited="7" lowestEdited="6" rupBuild="29929"/>
   <workbookPr/>
   <mc:AlternateContent xmlns:mc="http://schemas.openxmlformats.org/markup-compatibility/2006">
     <mc:Choice Requires="x15">
-      <x15ac:absPath xmlns:x15ac="http://schemas.microsoft.com/office/spreadsheetml/2010/11/ac" url="C:\Users\Geust\PycharmProjects\AlternativeData\data\commodity\"/>
+      <x15ac:absPath xmlns:x15ac="http://schemas.microsoft.com/office/spreadsheetml/2010/11/ac" url="C:\Users\krm\PycharmProjects\AlternativeData\data\commodity\"/>
     </mc:Choice>
   </mc:AlternateContent>
-  <xr:revisionPtr revIDLastSave="0" documentId="13_ncr:1_{E011A9D8-FD09-41B1-B4B3-DF26481A1E2A}" xr6:coauthVersionLast="47" xr6:coauthVersionMax="47" xr10:uidLastSave="{00000000-0000-0000-0000-000000000000}"/>
+  <xr:revisionPtr revIDLastSave="0" documentId="13_ncr:1_{1FDF50C1-8441-46E5-BFFD-4C72C4E2936B}" xr6:coauthVersionLast="47" xr6:coauthVersionMax="47" xr10:uidLastSave="{00000000-0000-0000-0000-000000000000}"/>
   <bookViews>
-    <workbookView xWindow="-110" yWindow="-110" windowWidth="23260" windowHeight="14860" xr2:uid="{00000000-000D-0000-FFFF-FFFF00000000}"/>
+    <workbookView xWindow="28680" yWindow="-120" windowWidth="29040" windowHeight="15720" xr2:uid="{00000000-000D-0000-FFFF-FFFF00000000}"/>
   </bookViews>
   <sheets>
     <sheet name="Lithium" sheetId="1" r:id="rId1"/>
@@ -36,7 +36,7 @@
 </file>
 
 <file path=xl/sharedStrings.xml><?xml version="1.0" encoding="utf-8"?>
-<sst xmlns="http://schemas.openxmlformats.org/spreadsheetml/2006/main" count="2267" uniqueCount="16">
+<sst xmlns="http://schemas.openxmlformats.org/spreadsheetml/2006/main" count="2268" uniqueCount="16">
   <si>
     <t>source</t>
     <phoneticPr fontId="2" type="noConversion"/>
@@ -241,9 +241,9 @@
     </xf>
   </cellXfs>
   <cellStyles count="3">
-    <cellStyle name="Comma" xfId="1" builtinId="3"/>
-    <cellStyle name="Hyperlink" xfId="2" builtinId="8"/>
-    <cellStyle name="Normal" xfId="0" builtinId="0"/>
+    <cellStyle name="쉼표" xfId="1" builtinId="3"/>
+    <cellStyle name="표준" xfId="0" builtinId="0"/>
+    <cellStyle name="하이퍼링크" xfId="2" builtinId="8"/>
   </cellStyles>
   <dxfs count="0"/>
   <tableStyles count="0" defaultTableStyle="TableStyleMedium2" defaultPivotStyle="PivotStyleLight16"/>
@@ -261,7 +261,7 @@
 <file path=xl/charts/chart1.xml><?xml version="1.0" encoding="utf-8"?>
 <c:chartSpace xmlns:c="http://schemas.openxmlformats.org/drawingml/2006/chart" xmlns:a="http://schemas.openxmlformats.org/drawingml/2006/main" xmlns:r="http://schemas.openxmlformats.org/officeDocument/2006/relationships" xmlns:c16r2="http://schemas.microsoft.com/office/drawing/2015/06/chart">
   <c:date1904 val="0"/>
-  <c:lang val="en-US"/>
+  <c:lang val="ko-KR"/>
   <c:roundedCorners val="0"/>
   <mc:AlternateContent xmlns:mc="http://schemas.openxmlformats.org/markup-compatibility/2006">
     <mc:Choice xmlns:c14="http://schemas.microsoft.com/office/drawing/2007/8/2/chart" Requires="c14">
@@ -7061,6 +7061,9 @@
                 <c:pt idx="2252">
                   <c:v>46167</c:v>
                 </c:pt>
+                <c:pt idx="2253">
+                  <c:v>46168</c:v>
+                </c:pt>
               </c:numCache>
             </c:numRef>
           </c:cat>
@@ -13828,6 +13831,9 @@
                 </c:pt>
                 <c:pt idx="2252">
                   <c:v>183250</c:v>
+                </c:pt>
+                <c:pt idx="2253">
+                  <c:v>180000</c:v>
                 </c:pt>
               </c:numCache>
             </c:numRef>
@@ -14907,15 +14913,15 @@
 
 <file path=xl/worksheets/sheet1.xml><?xml version="1.0" encoding="utf-8"?>
 <worksheet xmlns="http://schemas.openxmlformats.org/spreadsheetml/2006/main" xmlns:r="http://schemas.openxmlformats.org/officeDocument/2006/relationships" xmlns:mc="http://schemas.openxmlformats.org/markup-compatibility/2006" xmlns:x14ac="http://schemas.microsoft.com/office/spreadsheetml/2009/9/ac" xmlns:xr="http://schemas.microsoft.com/office/spreadsheetml/2014/revision" xmlns:xr2="http://schemas.microsoft.com/office/spreadsheetml/2015/revision2" xmlns:xr3="http://schemas.microsoft.com/office/spreadsheetml/2016/revision3" mc:Ignorable="x14ac xr xr2 xr3" xr:uid="{00000000-0001-0000-0000-000000000000}">
-  <dimension ref="A1:H2254"/>
-  <sheetFormatPr defaultColWidth="9" defaultRowHeight="13.5"/>
+  <dimension ref="A1:H2255"/>
+  <sheetFormatPr defaultColWidth="9" defaultRowHeight="12.6"/>
   <cols>
-    <col min="1" max="1" width="12.54296875" style="3" bestFit="1" customWidth="1"/>
-    <col min="2" max="2" width="14.08984375" style="9" bestFit="1" customWidth="1"/>
-    <col min="3" max="3" width="11.81640625" style="20" bestFit="1" customWidth="1"/>
-    <col min="4" max="4" width="11.54296875" style="11" customWidth="1"/>
-    <col min="5" max="7" width="11.54296875" style="16" customWidth="1"/>
-    <col min="8" max="8" width="10.81640625" style="10" bestFit="1" customWidth="1"/>
+    <col min="1" max="1" width="12.5546875" style="3" bestFit="1" customWidth="1"/>
+    <col min="2" max="2" width="14.109375" style="9" bestFit="1" customWidth="1"/>
+    <col min="3" max="3" width="11.77734375" style="20" bestFit="1" customWidth="1"/>
+    <col min="4" max="4" width="11.5546875" style="11" customWidth="1"/>
+    <col min="5" max="7" width="11.5546875" style="16" customWidth="1"/>
+    <col min="8" max="8" width="10.77734375" style="10" bestFit="1" customWidth="1"/>
     <col min="9" max="16384" width="9" style="7"/>
   </cols>
   <sheetData>
@@ -60831,6 +60837,32 @@
       </c>
       <c r="H2254" s="10">
         <v>183250</v>
+      </c>
+    </row>
+    <row r="2255" spans="1:8">
+      <c r="A2255" s="3">
+        <v>46168</v>
+      </c>
+      <c r="B2255" s="9">
+        <v>46168</v>
+      </c>
+      <c r="C2255" s="19">
+        <v>0.625</v>
+      </c>
+      <c r="D2255" s="4" t="s">
+        <v>10</v>
+      </c>
+      <c r="E2255" s="16">
+        <v>183232</v>
+      </c>
+      <c r="F2255" s="16">
+        <v>183287</v>
+      </c>
+      <c r="G2255" s="16">
+        <v>177000</v>
+      </c>
+      <c r="H2255" s="10">
+        <v>180000</v>
       </c>
     </row>
   </sheetData>
@@ -60843,9 +60875,9 @@
 <file path=xl/worksheets/sheet2.xml><?xml version="1.0" encoding="utf-8"?>
 <worksheet xmlns="http://schemas.openxmlformats.org/spreadsheetml/2006/main" xmlns:r="http://schemas.openxmlformats.org/officeDocument/2006/relationships" xmlns:mc="http://schemas.openxmlformats.org/markup-compatibility/2006" xmlns:x14ac="http://schemas.microsoft.com/office/spreadsheetml/2009/9/ac" xmlns:xr="http://schemas.microsoft.com/office/spreadsheetml/2014/revision" xmlns:xr2="http://schemas.microsoft.com/office/spreadsheetml/2015/revision2" xmlns:xr3="http://schemas.microsoft.com/office/spreadsheetml/2016/revision3" mc:Ignorable="x14ac xr xr2 xr3" xr:uid="{9FF8FA39-E640-4E6A-B261-45B6002B9973}">
   <dimension ref="B2:C4"/>
-  <sheetFormatPr defaultColWidth="8.90625" defaultRowHeight="14.5"/>
+  <sheetFormatPr defaultColWidth="8.88671875" defaultRowHeight="14.4"/>
   <cols>
-    <col min="2" max="2" width="10.453125" bestFit="1" customWidth="1"/>
+    <col min="2" max="2" width="10.44140625" bestFit="1" customWidth="1"/>
   </cols>
   <sheetData>
     <row r="2" spans="2:3">
@@ -60885,7 +60917,7 @@
 <file path=xl/worksheets/sheet3.xml><?xml version="1.0" encoding="utf-8"?>
 <worksheet xmlns="http://schemas.openxmlformats.org/spreadsheetml/2006/main" xmlns:r="http://schemas.openxmlformats.org/officeDocument/2006/relationships" xmlns:mc="http://schemas.openxmlformats.org/markup-compatibility/2006" xmlns:x14ac="http://schemas.microsoft.com/office/spreadsheetml/2009/9/ac" xmlns:xr="http://schemas.microsoft.com/office/spreadsheetml/2014/revision" xmlns:xr2="http://schemas.microsoft.com/office/spreadsheetml/2015/revision2" xmlns:xr3="http://schemas.microsoft.com/office/spreadsheetml/2016/revision3" mc:Ignorable="x14ac xr xr2 xr3" xr:uid="{17A1C1D3-27CA-4F31-B658-DBB84930A46D}">
   <dimension ref="A1"/>
-  <sheetFormatPr defaultColWidth="8.90625" defaultRowHeight="14.5"/>
+  <sheetFormatPr defaultColWidth="8.88671875" defaultRowHeight="14.4"/>
   <sheetData/>
   <phoneticPr fontId="2" type="noConversion"/>
   <pageMargins left="0.7" right="0.7" top="0.75" bottom="0.75" header="0.3" footer="0.3"/>

--- a/data/commodity/Lithium.xlsx
+++ b/data/commodity/Lithium.xlsx
@@ -8,7 +8,7 @@
       <x15ac:absPath xmlns:x15ac="http://schemas.microsoft.com/office/spreadsheetml/2010/11/ac" url="C:\Users\krm\PycharmProjects\AlternativeData\data\commodity\"/>
     </mc:Choice>
   </mc:AlternateContent>
-  <xr:revisionPtr revIDLastSave="0" documentId="13_ncr:1_{1FDF50C1-8441-46E5-BFFD-4C72C4E2936B}" xr6:coauthVersionLast="47" xr6:coauthVersionMax="47" xr10:uidLastSave="{00000000-0000-0000-0000-000000000000}"/>
+  <xr:revisionPtr revIDLastSave="0" documentId="13_ncr:1_{AB6D78D3-185D-4269-986D-2E8C5803DED9}" xr6:coauthVersionLast="47" xr6:coauthVersionMax="47" xr10:uidLastSave="{00000000-0000-0000-0000-000000000000}"/>
   <bookViews>
     <workbookView xWindow="28680" yWindow="-120" windowWidth="29040" windowHeight="15720" xr2:uid="{00000000-000D-0000-FFFF-FFFF00000000}"/>
   </bookViews>
@@ -36,7 +36,7 @@
 </file>
 
 <file path=xl/sharedStrings.xml><?xml version="1.0" encoding="utf-8"?>
-<sst xmlns="http://schemas.openxmlformats.org/spreadsheetml/2006/main" count="2268" uniqueCount="16">
+<sst xmlns="http://schemas.openxmlformats.org/spreadsheetml/2006/main" count="2269" uniqueCount="16">
   <si>
     <t>source</t>
     <phoneticPr fontId="2" type="noConversion"/>
@@ -7064,6 +7064,9 @@
                 <c:pt idx="2253">
                   <c:v>46168</c:v>
                 </c:pt>
+                <c:pt idx="2254">
+                  <c:v>46169</c:v>
+                </c:pt>
               </c:numCache>
             </c:numRef>
           </c:cat>
@@ -13834,6 +13837,9 @@
                 </c:pt>
                 <c:pt idx="2253">
                   <c:v>180000</c:v>
+                </c:pt>
+                <c:pt idx="2254">
+                  <c:v>177000</c:v>
                 </c:pt>
               </c:numCache>
             </c:numRef>
@@ -14913,7 +14919,7 @@
 
 <file path=xl/worksheets/sheet1.xml><?xml version="1.0" encoding="utf-8"?>
 <worksheet xmlns="http://schemas.openxmlformats.org/spreadsheetml/2006/main" xmlns:r="http://schemas.openxmlformats.org/officeDocument/2006/relationships" xmlns:mc="http://schemas.openxmlformats.org/markup-compatibility/2006" xmlns:x14ac="http://schemas.microsoft.com/office/spreadsheetml/2009/9/ac" xmlns:xr="http://schemas.microsoft.com/office/spreadsheetml/2014/revision" xmlns:xr2="http://schemas.microsoft.com/office/spreadsheetml/2015/revision2" xmlns:xr3="http://schemas.microsoft.com/office/spreadsheetml/2016/revision3" mc:Ignorable="x14ac xr xr2 xr3" xr:uid="{00000000-0001-0000-0000-000000000000}">
-  <dimension ref="A1:H2255"/>
+  <dimension ref="A1:H2256"/>
   <sheetFormatPr defaultColWidth="9" defaultRowHeight="12.6"/>
   <cols>
     <col min="1" max="1" width="12.5546875" style="3" bestFit="1" customWidth="1"/>
@@ -60863,6 +60869,32 @@
       </c>
       <c r="H2255" s="10">
         <v>180000</v>
+      </c>
+    </row>
+    <row r="2256" spans="1:8">
+      <c r="A2256" s="3">
+        <v>46169</v>
+      </c>
+      <c r="B2256" s="9">
+        <v>46169</v>
+      </c>
+      <c r="C2256" s="19">
+        <v>0.625</v>
+      </c>
+      <c r="D2256" s="4" t="s">
+        <v>10</v>
+      </c>
+      <c r="E2256" s="16">
+        <v>180036</v>
+      </c>
+      <c r="F2256" s="16">
+        <v>180036</v>
+      </c>
+      <c r="G2256" s="16">
+        <v>174000</v>
+      </c>
+      <c r="H2256" s="10">
+        <v>177000</v>
       </c>
     </row>
   </sheetData>

--- a/data/commodity/Lithium.xlsx
+++ b/data/commodity/Lithium.xlsx
@@ -8,7 +8,7 @@
       <x15ac:absPath xmlns:x15ac="http://schemas.microsoft.com/office/spreadsheetml/2010/11/ac" url="C:\Users\Geust\PycharmProjects\AlternativeData\data\commodity\"/>
     </mc:Choice>
   </mc:AlternateContent>
-  <xr:revisionPtr revIDLastSave="0" documentId="13_ncr:1_{4A2B524C-54C1-40A6-8812-B3AC3716C68B}" xr6:coauthVersionLast="47" xr6:coauthVersionMax="47" xr10:uidLastSave="{00000000-0000-0000-0000-000000000000}"/>
+  <xr:revisionPtr revIDLastSave="0" documentId="13_ncr:1_{A3998CDE-A840-4155-BE29-5F4E6EF60E01}" xr6:coauthVersionLast="47" xr6:coauthVersionMax="47" xr10:uidLastSave="{00000000-0000-0000-0000-000000000000}"/>
   <bookViews>
     <workbookView xWindow="-110" yWindow="-110" windowWidth="23260" windowHeight="14860" xr2:uid="{00000000-000D-0000-FFFF-FFFF00000000}"/>
   </bookViews>
@@ -36,7 +36,7 @@
 </file>
 
 <file path=xl/sharedStrings.xml><?xml version="1.0" encoding="utf-8"?>
-<sst xmlns="http://schemas.openxmlformats.org/spreadsheetml/2006/main" count="2270" uniqueCount="16">
+<sst xmlns="http://schemas.openxmlformats.org/spreadsheetml/2006/main" count="2271" uniqueCount="16">
   <si>
     <t>source</t>
     <phoneticPr fontId="2" type="noConversion"/>
@@ -7070,6 +7070,9 @@
                 <c:pt idx="2255">
                   <c:v>46170</c:v>
                 </c:pt>
+                <c:pt idx="2256">
+                  <c:v>46171</c:v>
+                </c:pt>
               </c:numCache>
             </c:numRef>
           </c:cat>
@@ -13846,6 +13849,9 @@
                 </c:pt>
                 <c:pt idx="2255">
                   <c:v>175500</c:v>
+                </c:pt>
+                <c:pt idx="2256">
+                  <c:v>177500</c:v>
                 </c:pt>
               </c:numCache>
             </c:numRef>
@@ -14925,7 +14931,7 @@
 
 <file path=xl/worksheets/sheet1.xml><?xml version="1.0" encoding="utf-8"?>
 <worksheet xmlns="http://schemas.openxmlformats.org/spreadsheetml/2006/main" xmlns:r="http://schemas.openxmlformats.org/officeDocument/2006/relationships" xmlns:mc="http://schemas.openxmlformats.org/markup-compatibility/2006" xmlns:x14ac="http://schemas.microsoft.com/office/spreadsheetml/2009/9/ac" xmlns:xr="http://schemas.microsoft.com/office/spreadsheetml/2014/revision" xmlns:xr2="http://schemas.microsoft.com/office/spreadsheetml/2015/revision2" xmlns:xr3="http://schemas.microsoft.com/office/spreadsheetml/2016/revision3" mc:Ignorable="x14ac xr xr2 xr3" xr:uid="{00000000-0001-0000-0000-000000000000}">
-  <dimension ref="A1:H2257"/>
+  <dimension ref="A1:H2258"/>
   <sheetFormatPr defaultColWidth="9" defaultRowHeight="13.5"/>
   <cols>
     <col min="1" max="1" width="12.54296875" style="3" bestFit="1" customWidth="1"/>
@@ -60927,6 +60933,32 @@
       </c>
       <c r="H2257" s="10">
         <v>175500</v>
+      </c>
+    </row>
+    <row r="2258" spans="1:8">
+      <c r="A2258" s="3">
+        <v>46171</v>
+      </c>
+      <c r="B2258" s="9">
+        <v>46171</v>
+      </c>
+      <c r="C2258" s="19">
+        <v>0.625</v>
+      </c>
+      <c r="D2258" s="4" t="s">
+        <v>10</v>
+      </c>
+      <c r="E2258" s="16">
+        <v>175535</v>
+      </c>
+      <c r="F2258" s="16">
+        <v>181000</v>
+      </c>
+      <c r="G2258" s="16">
+        <v>174000</v>
+      </c>
+      <c r="H2258" s="10">
+        <v>177500</v>
       </c>
     </row>
   </sheetData>

--- a/data/commodity/Lithium.xlsx
+++ b/data/commodity/Lithium.xlsx
@@ -5,12 +5,12 @@
   <workbookPr/>
   <mc:AlternateContent xmlns:mc="http://schemas.openxmlformats.org/markup-compatibility/2006">
     <mc:Choice Requires="x15">
-      <x15ac:absPath xmlns:x15ac="http://schemas.microsoft.com/office/spreadsheetml/2010/11/ac" url="C:\Users\Geust\PycharmProjects\AlternativeData\data\commodity\"/>
+      <x15ac:absPath xmlns:x15ac="http://schemas.microsoft.com/office/spreadsheetml/2010/11/ac" url="C:\Users\krm\PycharmProjects\AlternativeData\data\commodity\"/>
     </mc:Choice>
   </mc:AlternateContent>
-  <xr:revisionPtr revIDLastSave="0" documentId="13_ncr:1_{2AE3D593-AE88-491A-81D1-43D8A151AA6C}" xr6:coauthVersionLast="47" xr6:coauthVersionMax="47" xr10:uidLastSave="{00000000-0000-0000-0000-000000000000}"/>
+  <xr:revisionPtr revIDLastSave="0" documentId="13_ncr:1_{57BDF412-4116-4521-9177-9CBC12CCD82B}" xr6:coauthVersionLast="47" xr6:coauthVersionMax="47" xr10:uidLastSave="{00000000-0000-0000-0000-000000000000}"/>
   <bookViews>
-    <workbookView xWindow="760" yWindow="760" windowWidth="17280" windowHeight="10690" xr2:uid="{00000000-000D-0000-FFFF-FFFF00000000}"/>
+    <workbookView xWindow="28680" yWindow="-120" windowWidth="29040" windowHeight="15720" xr2:uid="{00000000-000D-0000-FFFF-FFFF00000000}"/>
   </bookViews>
   <sheets>
     <sheet name="Lithium" sheetId="1" r:id="rId1"/>
@@ -36,7 +36,7 @@
 </file>
 
 <file path=xl/sharedStrings.xml><?xml version="1.0" encoding="utf-8"?>
-<sst xmlns="http://schemas.openxmlformats.org/spreadsheetml/2006/main" count="2274" uniqueCount="16">
+<sst xmlns="http://schemas.openxmlformats.org/spreadsheetml/2006/main" count="2276" uniqueCount="16">
   <si>
     <t>source</t>
     <phoneticPr fontId="2" type="noConversion"/>
@@ -241,9 +241,9 @@
     </xf>
   </cellXfs>
   <cellStyles count="3">
-    <cellStyle name="Comma" xfId="1" builtinId="3"/>
-    <cellStyle name="Hyperlink" xfId="2" builtinId="8"/>
-    <cellStyle name="Normal" xfId="0" builtinId="0"/>
+    <cellStyle name="쉼표" xfId="1" builtinId="3"/>
+    <cellStyle name="표준" xfId="0" builtinId="0"/>
+    <cellStyle name="하이퍼링크" xfId="2" builtinId="8"/>
   </cellStyles>
   <dxfs count="0"/>
   <tableStyles count="0" defaultTableStyle="TableStyleMedium2" defaultPivotStyle="PivotStyleLight16"/>
@@ -261,7 +261,7 @@
 <file path=xl/charts/chart1.xml><?xml version="1.0" encoding="utf-8"?>
 <c:chartSpace xmlns:c="http://schemas.openxmlformats.org/drawingml/2006/chart" xmlns:a="http://schemas.openxmlformats.org/drawingml/2006/main" xmlns:r="http://schemas.openxmlformats.org/officeDocument/2006/relationships" xmlns:c16r2="http://schemas.microsoft.com/office/drawing/2015/06/chart">
   <c:date1904 val="0"/>
-  <c:lang val="en-US"/>
+  <c:lang val="ko-KR"/>
   <c:roundedCorners val="0"/>
   <mc:AlternateContent xmlns:mc="http://schemas.openxmlformats.org/markup-compatibility/2006">
     <mc:Choice xmlns:c14="http://schemas.microsoft.com/office/drawing/2007/8/2/chart" Requires="c14">
@@ -7082,6 +7082,12 @@
                 <c:pt idx="2259">
                   <c:v>46176</c:v>
                 </c:pt>
+                <c:pt idx="2260">
+                  <c:v>46177</c:v>
+                </c:pt>
+                <c:pt idx="2261">
+                  <c:v>46178</c:v>
+                </c:pt>
               </c:numCache>
             </c:numRef>
           </c:cat>
@@ -13870,6 +13876,12 @@
                 </c:pt>
                 <c:pt idx="2259">
                   <c:v>170500</c:v>
+                </c:pt>
+                <c:pt idx="2260">
+                  <c:v>168250</c:v>
+                </c:pt>
+                <c:pt idx="2261">
+                  <c:v>163000</c:v>
                 </c:pt>
               </c:numCache>
             </c:numRef>
@@ -14949,15 +14961,15 @@
 
 <file path=xl/worksheets/sheet1.xml><?xml version="1.0" encoding="utf-8"?>
 <worksheet xmlns="http://schemas.openxmlformats.org/spreadsheetml/2006/main" xmlns:r="http://schemas.openxmlformats.org/officeDocument/2006/relationships" xmlns:mc="http://schemas.openxmlformats.org/markup-compatibility/2006" xmlns:x14ac="http://schemas.microsoft.com/office/spreadsheetml/2009/9/ac" xmlns:xr="http://schemas.microsoft.com/office/spreadsheetml/2014/revision" xmlns:xr2="http://schemas.microsoft.com/office/spreadsheetml/2015/revision2" xmlns:xr3="http://schemas.microsoft.com/office/spreadsheetml/2016/revision3" mc:Ignorable="x14ac xr xr2 xr3" xr:uid="{00000000-0001-0000-0000-000000000000}">
-  <dimension ref="A1:H2261"/>
-  <sheetFormatPr defaultColWidth="9" defaultRowHeight="13.5"/>
+  <dimension ref="A1:H2263"/>
+  <sheetFormatPr defaultColWidth="9" defaultRowHeight="12.6"/>
   <cols>
-    <col min="1" max="1" width="12.54296875" style="3" bestFit="1" customWidth="1"/>
-    <col min="2" max="2" width="14.08984375" style="9" bestFit="1" customWidth="1"/>
-    <col min="3" max="3" width="11.81640625" style="20" bestFit="1" customWidth="1"/>
-    <col min="4" max="4" width="11.54296875" style="11" customWidth="1"/>
-    <col min="5" max="7" width="11.54296875" style="16" customWidth="1"/>
-    <col min="8" max="8" width="10.81640625" style="10" bestFit="1" customWidth="1"/>
+    <col min="1" max="1" width="12.5546875" style="3" bestFit="1" customWidth="1"/>
+    <col min="2" max="2" width="14.109375" style="9" bestFit="1" customWidth="1"/>
+    <col min="3" max="3" width="11.77734375" style="20" bestFit="1" customWidth="1"/>
+    <col min="4" max="4" width="11.5546875" style="11" customWidth="1"/>
+    <col min="5" max="7" width="11.5546875" style="16" customWidth="1"/>
+    <col min="8" max="8" width="10.77734375" style="10" bestFit="1" customWidth="1"/>
     <col min="9" max="16384" width="9" style="7"/>
   </cols>
   <sheetData>
@@ -61055,6 +61067,58 @@
       </c>
       <c r="H2261" s="10">
         <v>170500</v>
+      </c>
+    </row>
+    <row r="2262" spans="1:8">
+      <c r="A2262" s="3">
+        <v>46177</v>
+      </c>
+      <c r="B2262" s="9">
+        <v>46177</v>
+      </c>
+      <c r="C2262" s="19">
+        <v>0.625</v>
+      </c>
+      <c r="D2262" s="4" t="s">
+        <v>10</v>
+      </c>
+      <c r="E2262" s="16">
+        <v>168250</v>
+      </c>
+      <c r="F2262" s="16">
+        <v>172000</v>
+      </c>
+      <c r="G2262" s="16">
+        <v>164500</v>
+      </c>
+      <c r="H2262" s="10">
+        <v>168250</v>
+      </c>
+    </row>
+    <row r="2263" spans="1:8">
+      <c r="A2263" s="3">
+        <v>46178</v>
+      </c>
+      <c r="B2263" s="9">
+        <v>46178</v>
+      </c>
+      <c r="C2263" s="19">
+        <v>0.625</v>
+      </c>
+      <c r="D2263" s="4" t="s">
+        <v>10</v>
+      </c>
+      <c r="E2263" s="16">
+        <v>168284</v>
+      </c>
+      <c r="F2263" s="16">
+        <v>169000</v>
+      </c>
+      <c r="G2263" s="16">
+        <v>157000</v>
+      </c>
+      <c r="H2263" s="10">
+        <v>163000</v>
       </c>
     </row>
   </sheetData>
@@ -61067,9 +61131,9 @@
 <file path=xl/worksheets/sheet2.xml><?xml version="1.0" encoding="utf-8"?>
 <worksheet xmlns="http://schemas.openxmlformats.org/spreadsheetml/2006/main" xmlns:r="http://schemas.openxmlformats.org/officeDocument/2006/relationships" xmlns:mc="http://schemas.openxmlformats.org/markup-compatibility/2006" xmlns:x14ac="http://schemas.microsoft.com/office/spreadsheetml/2009/9/ac" xmlns:xr="http://schemas.microsoft.com/office/spreadsheetml/2014/revision" xmlns:xr2="http://schemas.microsoft.com/office/spreadsheetml/2015/revision2" xmlns:xr3="http://schemas.microsoft.com/office/spreadsheetml/2016/revision3" mc:Ignorable="x14ac xr xr2 xr3" xr:uid="{9FF8FA39-E640-4E6A-B261-45B6002B9973}">
   <dimension ref="B2:C4"/>
-  <sheetFormatPr defaultColWidth="8.90625" defaultRowHeight="14.5"/>
+  <sheetFormatPr defaultColWidth="8.88671875" defaultRowHeight="14.4"/>
   <cols>
-    <col min="2" max="2" width="10.453125" bestFit="1" customWidth="1"/>
+    <col min="2" max="2" width="10.44140625" bestFit="1" customWidth="1"/>
   </cols>
   <sheetData>
     <row r="2" spans="2:3">
@@ -61109,7 +61173,7 @@
 <file path=xl/worksheets/sheet3.xml><?xml version="1.0" encoding="utf-8"?>
 <worksheet xmlns="http://schemas.openxmlformats.org/spreadsheetml/2006/main" xmlns:r="http://schemas.openxmlformats.org/officeDocument/2006/relationships" xmlns:mc="http://schemas.openxmlformats.org/markup-compatibility/2006" xmlns:x14ac="http://schemas.microsoft.com/office/spreadsheetml/2009/9/ac" xmlns:xr="http://schemas.microsoft.com/office/spreadsheetml/2014/revision" xmlns:xr2="http://schemas.microsoft.com/office/spreadsheetml/2015/revision2" xmlns:xr3="http://schemas.microsoft.com/office/spreadsheetml/2016/revision3" mc:Ignorable="x14ac xr xr2 xr3" xr:uid="{17A1C1D3-27CA-4F31-B658-DBB84930A46D}">
   <dimension ref="A1"/>
-  <sheetFormatPr defaultColWidth="8.90625" defaultRowHeight="14.5"/>
+  <sheetFormatPr defaultColWidth="8.88671875" defaultRowHeight="14.4"/>
   <sheetData/>
   <phoneticPr fontId="2" type="noConversion"/>
   <pageMargins left="0.7" right="0.7" top="0.75" bottom="0.75" header="0.3" footer="0.3"/>

--- a/data/commodity/Lithium.xlsx
+++ b/data/commodity/Lithium.xlsx
@@ -8,7 +8,7 @@
       <x15ac:absPath xmlns:x15ac="http://schemas.microsoft.com/office/spreadsheetml/2010/11/ac" url="C:\Users\krm\PycharmProjects\AlternativeData\data\commodity\"/>
     </mc:Choice>
   </mc:AlternateContent>
-  <xr:revisionPtr revIDLastSave="0" documentId="13_ncr:1_{218F3DEE-B27E-4491-8335-2C04F0B10ADF}" xr6:coauthVersionLast="47" xr6:coauthVersionMax="47" xr10:uidLastSave="{00000000-0000-0000-0000-000000000000}"/>
+  <xr:revisionPtr revIDLastSave="0" documentId="13_ncr:1_{F4528ACF-096F-4E7A-AD99-DDA03420DB90}" xr6:coauthVersionLast="47" xr6:coauthVersionMax="47" xr10:uidLastSave="{00000000-0000-0000-0000-000000000000}"/>
   <bookViews>
     <workbookView xWindow="28680" yWindow="-120" windowWidth="29040" windowHeight="15720" xr2:uid="{00000000-000D-0000-FFFF-FFFF00000000}"/>
   </bookViews>
@@ -36,7 +36,7 @@
 </file>
 
 <file path=xl/sharedStrings.xml><?xml version="1.0" encoding="utf-8"?>
-<sst xmlns="http://schemas.openxmlformats.org/spreadsheetml/2006/main" count="2277" uniqueCount="16">
+<sst xmlns="http://schemas.openxmlformats.org/spreadsheetml/2006/main" count="2278" uniqueCount="16">
   <si>
     <t>source</t>
     <phoneticPr fontId="2" type="noConversion"/>
@@ -7091,6 +7091,9 @@
                 <c:pt idx="2262">
                   <c:v>46181</c:v>
                 </c:pt>
+                <c:pt idx="2263">
+                  <c:v>46182</c:v>
+                </c:pt>
               </c:numCache>
             </c:numRef>
           </c:cat>
@@ -13887,6 +13890,9 @@
                   <c:v>163000</c:v>
                 </c:pt>
                 <c:pt idx="2262">
+                  <c:v>163750</c:v>
+                </c:pt>
+                <c:pt idx="2263">
                   <c:v>163750</c:v>
                 </c:pt>
               </c:numCache>
@@ -14967,7 +14973,7 @@
 
 <file path=xl/worksheets/sheet1.xml><?xml version="1.0" encoding="utf-8"?>
 <worksheet xmlns="http://schemas.openxmlformats.org/spreadsheetml/2006/main" xmlns:r="http://schemas.openxmlformats.org/officeDocument/2006/relationships" xmlns:mc="http://schemas.openxmlformats.org/markup-compatibility/2006" xmlns:x14ac="http://schemas.microsoft.com/office/spreadsheetml/2009/9/ac" xmlns:xr="http://schemas.microsoft.com/office/spreadsheetml/2014/revision" xmlns:xr2="http://schemas.microsoft.com/office/spreadsheetml/2015/revision2" xmlns:xr3="http://schemas.microsoft.com/office/spreadsheetml/2016/revision3" mc:Ignorable="x14ac xr xr2 xr3" xr:uid="{00000000-0001-0000-0000-000000000000}">
-  <dimension ref="A1:H2264"/>
+  <dimension ref="A1:H2265"/>
   <sheetFormatPr defaultColWidth="9" defaultRowHeight="12.6"/>
   <cols>
     <col min="1" max="1" width="12.5546875" style="3" bestFit="1" customWidth="1"/>
@@ -61150,6 +61156,32 @@
         <v>162000</v>
       </c>
       <c r="H2264" s="10">
+        <v>163750</v>
+      </c>
+    </row>
+    <row r="2265" spans="1:8">
+      <c r="A2265" s="3">
+        <v>46182</v>
+      </c>
+      <c r="B2265" s="3">
+        <v>46182</v>
+      </c>
+      <c r="C2265" s="19">
+        <v>0.625</v>
+      </c>
+      <c r="D2265" s="4" t="s">
+        <v>10</v>
+      </c>
+      <c r="E2265" s="16">
+        <v>163717</v>
+      </c>
+      <c r="F2265" s="16">
+        <v>166500</v>
+      </c>
+      <c r="G2265" s="16">
+        <v>161000</v>
+      </c>
+      <c r="H2265" s="10">
         <v>163750</v>
       </c>
     </row>

--- a/data/commodity/Lithium.xlsx
+++ b/data/commodity/Lithium.xlsx
@@ -5,12 +5,12 @@
   <workbookPr/>
   <mc:AlternateContent xmlns:mc="http://schemas.openxmlformats.org/markup-compatibility/2006">
     <mc:Choice Requires="x15">
-      <x15ac:absPath xmlns:x15ac="http://schemas.microsoft.com/office/spreadsheetml/2010/11/ac" url="C:\Users\krm\PycharmProjects\AlternativeData\data\commodity\"/>
+      <x15ac:absPath xmlns:x15ac="http://schemas.microsoft.com/office/spreadsheetml/2010/11/ac" url="C:\Users\Geust\PycharmProjects\AlternativeData\data\commodity\"/>
     </mc:Choice>
   </mc:AlternateContent>
-  <xr:revisionPtr revIDLastSave="0" documentId="13_ncr:1_{F4528ACF-096F-4E7A-AD99-DDA03420DB90}" xr6:coauthVersionLast="47" xr6:coauthVersionMax="47" xr10:uidLastSave="{00000000-0000-0000-0000-000000000000}"/>
+  <xr:revisionPtr revIDLastSave="0" documentId="13_ncr:1_{E1949CB9-24FF-4147-B943-61C2ADE4EE16}" xr6:coauthVersionLast="47" xr6:coauthVersionMax="47" xr10:uidLastSave="{00000000-0000-0000-0000-000000000000}"/>
   <bookViews>
-    <workbookView xWindow="28680" yWindow="-120" windowWidth="29040" windowHeight="15720" xr2:uid="{00000000-000D-0000-FFFF-FFFF00000000}"/>
+    <workbookView xWindow="11430" yWindow="0" windowWidth="11700" windowHeight="14730" xr2:uid="{00000000-000D-0000-FFFF-FFFF00000000}"/>
   </bookViews>
   <sheets>
     <sheet name="Lithium" sheetId="1" r:id="rId1"/>
@@ -36,7 +36,7 @@
 </file>
 
 <file path=xl/sharedStrings.xml><?xml version="1.0" encoding="utf-8"?>
-<sst xmlns="http://schemas.openxmlformats.org/spreadsheetml/2006/main" count="2278" uniqueCount="16">
+<sst xmlns="http://schemas.openxmlformats.org/spreadsheetml/2006/main" count="2279" uniqueCount="16">
   <si>
     <t>source</t>
     <phoneticPr fontId="2" type="noConversion"/>
@@ -81,24 +81,20 @@
     <t>UTC+8</t>
   </si>
   <si>
-    <t>Close</t>
+    <t>https://tradingeconomics.com/commodity/lithium</t>
     <phoneticPr fontId="2" type="noConversion"/>
   </si>
   <si>
-    <t>Open</t>
-    <phoneticPr fontId="2" type="noConversion"/>
+    <t>open</t>
   </si>
   <si>
-    <t>High</t>
-    <phoneticPr fontId="2" type="noConversion"/>
+    <t>high</t>
   </si>
   <si>
-    <t>Low</t>
-    <phoneticPr fontId="2" type="noConversion"/>
+    <t>low</t>
   </si>
   <si>
-    <t>https://tradingeconomics.com/commodity/lithium</t>
-    <phoneticPr fontId="2" type="noConversion"/>
+    <t>close</t>
   </si>
 </sst>
 </file>
@@ -241,9 +237,9 @@
     </xf>
   </cellXfs>
   <cellStyles count="3">
-    <cellStyle name="쉼표" xfId="1" builtinId="3"/>
-    <cellStyle name="표준" xfId="0" builtinId="0"/>
-    <cellStyle name="하이퍼링크" xfId="2" builtinId="8"/>
+    <cellStyle name="Comma" xfId="1" builtinId="3"/>
+    <cellStyle name="Hyperlink" xfId="2" builtinId="8"/>
+    <cellStyle name="Normal" xfId="0" builtinId="0"/>
   </cellStyles>
   <dxfs count="0"/>
   <tableStyles count="0" defaultTableStyle="TableStyleMedium2" defaultPivotStyle="PivotStyleLight16"/>
@@ -261,7 +257,7 @@
 <file path=xl/charts/chart1.xml><?xml version="1.0" encoding="utf-8"?>
 <c:chartSpace xmlns:c="http://schemas.openxmlformats.org/drawingml/2006/chart" xmlns:a="http://schemas.openxmlformats.org/drawingml/2006/main" xmlns:r="http://schemas.openxmlformats.org/officeDocument/2006/relationships" xmlns:c16r2="http://schemas.microsoft.com/office/drawing/2015/06/chart">
   <c:date1904 val="0"/>
-  <c:lang val="ko-KR"/>
+  <c:lang val="en-US"/>
   <c:roundedCorners val="0"/>
   <mc:AlternateContent xmlns:mc="http://schemas.openxmlformats.org/markup-compatibility/2006">
     <mc:Choice xmlns:c14="http://schemas.microsoft.com/office/drawing/2007/8/2/chart" Requires="c14">
@@ -7094,6 +7090,9 @@
                 <c:pt idx="2263">
                   <c:v>46182</c:v>
                 </c:pt>
+                <c:pt idx="2264">
+                  <c:v>46183</c:v>
+                </c:pt>
               </c:numCache>
             </c:numRef>
           </c:cat>
@@ -13894,6 +13893,9 @@
                 </c:pt>
                 <c:pt idx="2263">
                   <c:v>163750</c:v>
+                </c:pt>
+                <c:pt idx="2264">
+                  <c:v>165750</c:v>
                 </c:pt>
               </c:numCache>
             </c:numRef>
@@ -14973,15 +14975,15 @@
 
 <file path=xl/worksheets/sheet1.xml><?xml version="1.0" encoding="utf-8"?>
 <worksheet xmlns="http://schemas.openxmlformats.org/spreadsheetml/2006/main" xmlns:r="http://schemas.openxmlformats.org/officeDocument/2006/relationships" xmlns:mc="http://schemas.openxmlformats.org/markup-compatibility/2006" xmlns:x14ac="http://schemas.microsoft.com/office/spreadsheetml/2009/9/ac" xmlns:xr="http://schemas.microsoft.com/office/spreadsheetml/2014/revision" xmlns:xr2="http://schemas.microsoft.com/office/spreadsheetml/2015/revision2" xmlns:xr3="http://schemas.microsoft.com/office/spreadsheetml/2016/revision3" mc:Ignorable="x14ac xr xr2 xr3" xr:uid="{00000000-0001-0000-0000-000000000000}">
-  <dimension ref="A1:H2265"/>
-  <sheetFormatPr defaultColWidth="9" defaultRowHeight="12.6"/>
+  <dimension ref="A1:H2266"/>
+  <sheetFormatPr defaultColWidth="9" defaultRowHeight="13.5"/>
   <cols>
-    <col min="1" max="1" width="12.5546875" style="3" bestFit="1" customWidth="1"/>
-    <col min="2" max="2" width="14.109375" style="9" bestFit="1" customWidth="1"/>
-    <col min="3" max="3" width="11.77734375" style="20" bestFit="1" customWidth="1"/>
-    <col min="4" max="4" width="11.5546875" style="11" customWidth="1"/>
-    <col min="5" max="7" width="11.5546875" style="16" customWidth="1"/>
-    <col min="8" max="8" width="10.77734375" style="10" bestFit="1" customWidth="1"/>
+    <col min="1" max="1" width="12.54296875" style="3" bestFit="1" customWidth="1"/>
+    <col min="2" max="2" width="14.08984375" style="9" bestFit="1" customWidth="1"/>
+    <col min="3" max="3" width="11.81640625" style="20" bestFit="1" customWidth="1"/>
+    <col min="4" max="4" width="11.54296875" style="11" customWidth="1"/>
+    <col min="5" max="7" width="11.54296875" style="16" customWidth="1"/>
+    <col min="8" max="8" width="10.81640625" style="10" bestFit="1" customWidth="1"/>
     <col min="9" max="16384" width="9" style="7"/>
   </cols>
   <sheetData>
@@ -15008,7 +15010,7 @@
         <v>14</v>
       </c>
       <c r="H1" s="6" t="s">
-        <v>11</v>
+        <v>15</v>
       </c>
     </row>
     <row r="2" spans="1:8">
@@ -61183,6 +61185,32 @@
       </c>
       <c r="H2265" s="10">
         <v>163750</v>
+      </c>
+    </row>
+    <row r="2266" spans="1:8">
+      <c r="A2266" s="3">
+        <v>46183</v>
+      </c>
+      <c r="B2266" s="9">
+        <v>46183</v>
+      </c>
+      <c r="C2266" s="19">
+        <v>0.625</v>
+      </c>
+      <c r="D2266" s="4" t="s">
+        <v>10</v>
+      </c>
+      <c r="E2266" s="16">
+        <v>163734</v>
+      </c>
+      <c r="F2266" s="16">
+        <v>168500</v>
+      </c>
+      <c r="G2266" s="16">
+        <v>163000</v>
+      </c>
+      <c r="H2266" s="10">
+        <v>165750</v>
       </c>
     </row>
   </sheetData>
@@ -61195,9 +61223,9 @@
 <file path=xl/worksheets/sheet2.xml><?xml version="1.0" encoding="utf-8"?>
 <worksheet xmlns="http://schemas.openxmlformats.org/spreadsheetml/2006/main" xmlns:r="http://schemas.openxmlformats.org/officeDocument/2006/relationships" xmlns:mc="http://schemas.openxmlformats.org/markup-compatibility/2006" xmlns:x14ac="http://schemas.microsoft.com/office/spreadsheetml/2009/9/ac" xmlns:xr="http://schemas.microsoft.com/office/spreadsheetml/2014/revision" xmlns:xr2="http://schemas.microsoft.com/office/spreadsheetml/2015/revision2" xmlns:xr3="http://schemas.microsoft.com/office/spreadsheetml/2016/revision3" mc:Ignorable="x14ac xr xr2 xr3" xr:uid="{9FF8FA39-E640-4E6A-B261-45B6002B9973}">
   <dimension ref="B2:C4"/>
-  <sheetFormatPr defaultColWidth="8.88671875" defaultRowHeight="14.4"/>
+  <sheetFormatPr defaultColWidth="8.90625" defaultRowHeight="14.5"/>
   <cols>
-    <col min="2" max="2" width="10.44140625" bestFit="1" customWidth="1"/>
+    <col min="2" max="2" width="10.453125" bestFit="1" customWidth="1"/>
   </cols>
   <sheetData>
     <row r="2" spans="2:3">
@@ -61205,7 +61233,7 @@
         <v>0</v>
       </c>
       <c r="C2" s="2" t="s">
-        <v>15</v>
+        <v>11</v>
       </c>
     </row>
     <row r="3" spans="2:3">
@@ -61237,7 +61265,7 @@
 <file path=xl/worksheets/sheet3.xml><?xml version="1.0" encoding="utf-8"?>
 <worksheet xmlns="http://schemas.openxmlformats.org/spreadsheetml/2006/main" xmlns:r="http://schemas.openxmlformats.org/officeDocument/2006/relationships" xmlns:mc="http://schemas.openxmlformats.org/markup-compatibility/2006" xmlns:x14ac="http://schemas.microsoft.com/office/spreadsheetml/2009/9/ac" xmlns:xr="http://schemas.microsoft.com/office/spreadsheetml/2014/revision" xmlns:xr2="http://schemas.microsoft.com/office/spreadsheetml/2015/revision2" xmlns:xr3="http://schemas.microsoft.com/office/spreadsheetml/2016/revision3" mc:Ignorable="x14ac xr xr2 xr3" xr:uid="{17A1C1D3-27CA-4F31-B658-DBB84930A46D}">
   <dimension ref="A1"/>
-  <sheetFormatPr defaultColWidth="8.88671875" defaultRowHeight="14.4"/>
+  <sheetFormatPr defaultColWidth="8.90625" defaultRowHeight="14.5"/>
   <sheetData/>
   <phoneticPr fontId="2" type="noConversion"/>
   <pageMargins left="0.7" right="0.7" top="0.75" bottom="0.75" header="0.3" footer="0.3"/>

--- a/data/commodity/Lithium.xlsx
+++ b/data/commodity/Lithium.xlsx
@@ -8,7 +8,7 @@
       <x15ac:absPath xmlns:x15ac="http://schemas.microsoft.com/office/spreadsheetml/2010/11/ac" url="/Users/tommy/Desktop/Pycharm/FinancialData/data/commodity/"/>
     </mc:Choice>
   </mc:AlternateContent>
-  <xr:revisionPtr revIDLastSave="0" documentId="13_ncr:1_{888AE553-65F6-484C-80CC-BC8EEF512A00}" xr6:coauthVersionLast="47" xr6:coauthVersionMax="47" xr10:uidLastSave="{00000000-0000-0000-0000-000000000000}"/>
+  <xr:revisionPtr revIDLastSave="0" documentId="13_ncr:1_{084CCFFA-A0B6-B349-8F99-AFFE6903EF8E}" xr6:coauthVersionLast="47" xr6:coauthVersionMax="47" xr10:uidLastSave="{00000000-0000-0000-0000-000000000000}"/>
   <bookViews>
     <workbookView xWindow="22160" yWindow="600" windowWidth="29040" windowHeight="15720" xr2:uid="{00000000-000D-0000-FFFF-FFFF00000000}"/>
   </bookViews>
@@ -36,7 +36,7 @@
 </file>
 
 <file path=xl/sharedStrings.xml><?xml version="1.0" encoding="utf-8"?>
-<sst xmlns="http://schemas.openxmlformats.org/spreadsheetml/2006/main" count="2282" uniqueCount="16">
+<sst xmlns="http://schemas.openxmlformats.org/spreadsheetml/2006/main" count="2283" uniqueCount="16">
   <si>
     <t>source</t>
     <phoneticPr fontId="2" type="noConversion"/>
@@ -7096,6 +7096,9 @@
                 <c:pt idx="2267">
                   <c:v>46188</c:v>
                 </c:pt>
+                <c:pt idx="2268">
+                  <c:v>46189</c:v>
+                </c:pt>
               </c:numCache>
             </c:numRef>
           </c:cat>
@@ -13908,6 +13911,9 @@
                 </c:pt>
                 <c:pt idx="2267">
                   <c:v>170500</c:v>
+                </c:pt>
+                <c:pt idx="2268">
+                  <c:v>169000</c:v>
                 </c:pt>
               </c:numCache>
             </c:numRef>
@@ -14987,7 +14993,7 @@
 
 <file path=xl/worksheets/sheet1.xml><?xml version="1.0" encoding="utf-8"?>
 <worksheet xmlns="http://schemas.openxmlformats.org/spreadsheetml/2006/main" xmlns:r="http://schemas.openxmlformats.org/officeDocument/2006/relationships" xmlns:mc="http://schemas.openxmlformats.org/markup-compatibility/2006" xmlns:x14ac="http://schemas.microsoft.com/office/spreadsheetml/2009/9/ac" xmlns:xr="http://schemas.microsoft.com/office/spreadsheetml/2014/revision" xmlns:xr2="http://schemas.microsoft.com/office/spreadsheetml/2015/revision2" xmlns:xr3="http://schemas.microsoft.com/office/spreadsheetml/2016/revision3" mc:Ignorable="x14ac xr xr2 xr3" xr:uid="{00000000-0001-0000-0000-000000000000}">
-  <dimension ref="A1:H2269"/>
+  <dimension ref="A1:H2270"/>
   <sheetFormatPr baseColWidth="10" defaultColWidth="9" defaultRowHeight="15" x14ac:dyDescent="0.2"/>
   <cols>
     <col min="1" max="1" width="10.33203125" style="16" bestFit="1" customWidth="1"/>
@@ -61300,6 +61306,32 @@
       </c>
       <c r="H2269" s="15">
         <v>170500</v>
+      </c>
+    </row>
+    <row r="2270" spans="1:8" x14ac:dyDescent="0.2">
+      <c r="A2270" s="16">
+        <v>46189</v>
+      </c>
+      <c r="B2270" s="14">
+        <v>46189</v>
+      </c>
+      <c r="C2270" s="10">
+        <v>0.625</v>
+      </c>
+      <c r="D2270" s="9" t="s">
+        <v>10</v>
+      </c>
+      <c r="E2270" s="17">
+        <v>170483</v>
+      </c>
+      <c r="F2270" s="17">
+        <v>172000</v>
+      </c>
+      <c r="G2270" s="17">
+        <v>166000</v>
+      </c>
+      <c r="H2270" s="15">
+        <v>169000</v>
       </c>
     </row>
   </sheetData>

--- a/data/commodity/Lithium.xlsx
+++ b/data/commodity/Lithium.xlsx
@@ -8,7 +8,7 @@
       <x15ac:absPath xmlns:x15ac="http://schemas.microsoft.com/office/spreadsheetml/2010/11/ac" url="/Users/tommy/Desktop/Pycharm/FinancialData/data/commodity/"/>
     </mc:Choice>
   </mc:AlternateContent>
-  <xr:revisionPtr revIDLastSave="0" documentId="13_ncr:1_{084CCFFA-A0B6-B349-8F99-AFFE6903EF8E}" xr6:coauthVersionLast="47" xr6:coauthVersionMax="47" xr10:uidLastSave="{00000000-0000-0000-0000-000000000000}"/>
+  <xr:revisionPtr revIDLastSave="0" documentId="13_ncr:1_{F4ABE03C-8FB7-6445-AFC3-D92438B9F552}" xr6:coauthVersionLast="47" xr6:coauthVersionMax="47" xr10:uidLastSave="{00000000-0000-0000-0000-000000000000}"/>
   <bookViews>
     <workbookView xWindow="22160" yWindow="600" windowWidth="29040" windowHeight="15720" xr2:uid="{00000000-000D-0000-FFFF-FFFF00000000}"/>
   </bookViews>
@@ -36,7 +36,7 @@
 </file>
 
 <file path=xl/sharedStrings.xml><?xml version="1.0" encoding="utf-8"?>
-<sst xmlns="http://schemas.openxmlformats.org/spreadsheetml/2006/main" count="2283" uniqueCount="16">
+<sst xmlns="http://schemas.openxmlformats.org/spreadsheetml/2006/main" count="2284" uniqueCount="16">
   <si>
     <t>source</t>
     <phoneticPr fontId="2" type="noConversion"/>
@@ -7099,6 +7099,9 @@
                 <c:pt idx="2268">
                   <c:v>46189</c:v>
                 </c:pt>
+                <c:pt idx="2269">
+                  <c:v>46190</c:v>
+                </c:pt>
               </c:numCache>
             </c:numRef>
           </c:cat>
@@ -13914,6 +13917,9 @@
                 </c:pt>
                 <c:pt idx="2268">
                   <c:v>169000</c:v>
+                </c:pt>
+                <c:pt idx="2269">
+                  <c:v>169500</c:v>
                 </c:pt>
               </c:numCache>
             </c:numRef>
@@ -14993,7 +14999,7 @@
 
 <file path=xl/worksheets/sheet1.xml><?xml version="1.0" encoding="utf-8"?>
 <worksheet xmlns="http://schemas.openxmlformats.org/spreadsheetml/2006/main" xmlns:r="http://schemas.openxmlformats.org/officeDocument/2006/relationships" xmlns:mc="http://schemas.openxmlformats.org/markup-compatibility/2006" xmlns:x14ac="http://schemas.microsoft.com/office/spreadsheetml/2009/9/ac" xmlns:xr="http://schemas.microsoft.com/office/spreadsheetml/2014/revision" xmlns:xr2="http://schemas.microsoft.com/office/spreadsheetml/2015/revision2" xmlns:xr3="http://schemas.microsoft.com/office/spreadsheetml/2016/revision3" mc:Ignorable="x14ac xr xr2 xr3" xr:uid="{00000000-0001-0000-0000-000000000000}">
-  <dimension ref="A1:H2270"/>
+  <dimension ref="A1:H2271"/>
   <sheetFormatPr baseColWidth="10" defaultColWidth="9" defaultRowHeight="15" x14ac:dyDescent="0.2"/>
   <cols>
     <col min="1" max="1" width="10.33203125" style="16" bestFit="1" customWidth="1"/>
@@ -61332,6 +61338,32 @@
       </c>
       <c r="H2270" s="15">
         <v>169000</v>
+      </c>
+    </row>
+    <row r="2271" spans="1:8" x14ac:dyDescent="0.2">
+      <c r="A2271" s="16">
+        <v>46190</v>
+      </c>
+      <c r="B2271" s="14">
+        <v>46190</v>
+      </c>
+      <c r="C2271" s="10">
+        <v>0.625</v>
+      </c>
+      <c r="D2271" s="9" t="s">
+        <v>10</v>
+      </c>
+      <c r="E2271" s="17">
+        <v>169034</v>
+      </c>
+      <c r="F2271" s="17">
+        <v>173000</v>
+      </c>
+      <c r="G2271" s="17">
+        <v>166000</v>
+      </c>
+      <c r="H2271" s="15">
+        <v>169500</v>
       </c>
     </row>
   </sheetData>

--- a/data/commodity/Lithium.xlsx
+++ b/data/commodity/Lithium.xlsx
@@ -8,7 +8,7 @@
       <x15ac:absPath xmlns:x15ac="http://schemas.microsoft.com/office/spreadsheetml/2010/11/ac" url="C:\Users\krm\PycharmProjects\AlternativeData\data\commodity\"/>
     </mc:Choice>
   </mc:AlternateContent>
-  <xr:revisionPtr revIDLastSave="0" documentId="13_ncr:1_{898932E9-BECE-4245-A4B1-3DEBCD79D1C4}" xr6:coauthVersionLast="47" xr6:coauthVersionMax="47" xr10:uidLastSave="{00000000-0000-0000-0000-000000000000}"/>
+  <xr:revisionPtr revIDLastSave="0" documentId="13_ncr:1_{654AC4EE-463A-4650-82DD-5F99348623AF}" xr6:coauthVersionLast="47" xr6:coauthVersionMax="47" xr10:uidLastSave="{00000000-0000-0000-0000-000000000000}"/>
   <bookViews>
     <workbookView xWindow="28680" yWindow="-120" windowWidth="29040" windowHeight="15720" xr2:uid="{00000000-000D-0000-FFFF-FFFF00000000}"/>
   </bookViews>
@@ -15008,9 +15008,9 @@
   <dimension ref="A1:H2272"/>
   <sheetFormatPr defaultColWidth="9" defaultRowHeight="14.4"/>
   <cols>
-    <col min="1" max="1" width="10.33203125" style="16" bestFit="1" customWidth="1"/>
+    <col min="1" max="1" width="10.77734375" style="16" bestFit="1" customWidth="1"/>
     <col min="2" max="2" width="12.109375" style="14" bestFit="1" customWidth="1"/>
-    <col min="3" max="3" width="10.109375" style="18" bestFit="1" customWidth="1"/>
+    <col min="3" max="3" width="10.6640625" style="18" bestFit="1" customWidth="1"/>
     <col min="4" max="4" width="10" style="19" bestFit="1" customWidth="1"/>
     <col min="5" max="7" width="11.44140625" style="17" customWidth="1"/>
     <col min="8" max="8" width="10.77734375" style="15" bestFit="1" customWidth="1"/>

--- a/data/commodity/Lithium.xlsx
+++ b/data/commodity/Lithium.xlsx
@@ -8,7 +8,7 @@
       <x15ac:absPath xmlns:x15ac="http://schemas.microsoft.com/office/spreadsheetml/2010/11/ac" url="C:\Users\krm\PycharmProjects\AlternativeData\data\commodity\"/>
     </mc:Choice>
   </mc:AlternateContent>
-  <xr:revisionPtr revIDLastSave="0" documentId="13_ncr:1_{875614C3-6DFB-4E89-BC85-CE33F8F29538}" xr6:coauthVersionLast="47" xr6:coauthVersionMax="47" xr10:uidLastSave="{00000000-0000-0000-0000-000000000000}"/>
+  <xr:revisionPtr revIDLastSave="0" documentId="13_ncr:1_{29B96CF7-7F84-4BF3-875E-9FBD68795B31}" xr6:coauthVersionLast="47" xr6:coauthVersionMax="47" xr10:uidLastSave="{00000000-0000-0000-0000-000000000000}"/>
   <bookViews>
     <workbookView xWindow="28680" yWindow="-120" windowWidth="29040" windowHeight="15720" xr2:uid="{00000000-000D-0000-FFFF-FFFF00000000}"/>
   </bookViews>
@@ -36,7 +36,7 @@
 </file>
 
 <file path=xl/sharedStrings.xml><?xml version="1.0" encoding="utf-8"?>
-<sst xmlns="http://schemas.openxmlformats.org/spreadsheetml/2006/main" count="2288" uniqueCount="16">
+<sst xmlns="http://schemas.openxmlformats.org/spreadsheetml/2006/main" count="2289" uniqueCount="16">
   <si>
     <t>source</t>
     <phoneticPr fontId="2" type="noConversion"/>
@@ -7114,6 +7114,9 @@
                 <c:pt idx="2273">
                   <c:v>46197</c:v>
                 </c:pt>
+                <c:pt idx="2274">
+                  <c:v>46198</c:v>
+                </c:pt>
               </c:numCache>
             </c:numRef>
           </c:cat>
@@ -13944,6 +13947,9 @@
                 </c:pt>
                 <c:pt idx="2273">
                   <c:v>157500</c:v>
+                </c:pt>
+                <c:pt idx="2274">
+                  <c:v>157000</c:v>
                 </c:pt>
               </c:numCache>
             </c:numRef>
@@ -15023,7 +15029,7 @@
 
 <file path=xl/worksheets/sheet1.xml><?xml version="1.0" encoding="utf-8"?>
 <worksheet xmlns="http://schemas.openxmlformats.org/spreadsheetml/2006/main" xmlns:r="http://schemas.openxmlformats.org/officeDocument/2006/relationships" xmlns:mc="http://schemas.openxmlformats.org/markup-compatibility/2006" xmlns:x14ac="http://schemas.microsoft.com/office/spreadsheetml/2009/9/ac" xmlns:xr="http://schemas.microsoft.com/office/spreadsheetml/2014/revision" xmlns:xr2="http://schemas.microsoft.com/office/spreadsheetml/2015/revision2" xmlns:xr3="http://schemas.microsoft.com/office/spreadsheetml/2016/revision3" mc:Ignorable="x14ac xr xr2 xr3" xr:uid="{00000000-0001-0000-0000-000000000000}">
-  <dimension ref="A1:H2275"/>
+  <dimension ref="A1:H2276"/>
   <sheetFormatPr defaultColWidth="9" defaultRowHeight="14.4"/>
   <cols>
     <col min="1" max="1" width="10.77734375" style="16" bestFit="1" customWidth="1"/>
@@ -61492,6 +61498,32 @@
       </c>
       <c r="H2275" s="15">
         <v>157500</v>
+      </c>
+    </row>
+    <row r="2276" spans="1:8">
+      <c r="A2276" s="16">
+        <v>46198</v>
+      </c>
+      <c r="B2276" s="16">
+        <v>46198</v>
+      </c>
+      <c r="C2276" s="10">
+        <v>0.625</v>
+      </c>
+      <c r="D2276" s="9" t="s">
+        <v>10</v>
+      </c>
+      <c r="E2276" s="17">
+        <v>157532</v>
+      </c>
+      <c r="F2276" s="17">
+        <v>161000</v>
+      </c>
+      <c r="G2276" s="17">
+        <v>153000</v>
+      </c>
+      <c r="H2276" s="15">
+        <v>157000</v>
       </c>
     </row>
   </sheetData>

--- a/data/commodity/Lithium.xlsx
+++ b/data/commodity/Lithium.xlsx
@@ -8,7 +8,7 @@
       <x15ac:absPath xmlns:x15ac="http://schemas.microsoft.com/office/spreadsheetml/2010/11/ac" url="C:\Users\krm\PycharmProjects\AlternativeData\data\commodity\"/>
     </mc:Choice>
   </mc:AlternateContent>
-  <xr:revisionPtr revIDLastSave="0" documentId="13_ncr:1_{29B96CF7-7F84-4BF3-875E-9FBD68795B31}" xr6:coauthVersionLast="47" xr6:coauthVersionMax="47" xr10:uidLastSave="{00000000-0000-0000-0000-000000000000}"/>
+  <xr:revisionPtr revIDLastSave="0" documentId="13_ncr:1_{BA2A05DB-CBC6-4276-92D2-B664D84FC248}" xr6:coauthVersionLast="47" xr6:coauthVersionMax="47" xr10:uidLastSave="{00000000-0000-0000-0000-000000000000}"/>
   <bookViews>
     <workbookView xWindow="28680" yWindow="-120" windowWidth="29040" windowHeight="15720" xr2:uid="{00000000-000D-0000-FFFF-FFFF00000000}"/>
   </bookViews>
@@ -36,7 +36,7 @@
 </file>
 
 <file path=xl/sharedStrings.xml><?xml version="1.0" encoding="utf-8"?>
-<sst xmlns="http://schemas.openxmlformats.org/spreadsheetml/2006/main" count="2289" uniqueCount="16">
+<sst xmlns="http://schemas.openxmlformats.org/spreadsheetml/2006/main" count="2291" uniqueCount="16">
   <si>
     <t>source</t>
     <phoneticPr fontId="2" type="noConversion"/>
@@ -7117,6 +7117,12 @@
                 <c:pt idx="2274">
                   <c:v>46198</c:v>
                 </c:pt>
+                <c:pt idx="2275">
+                  <c:v>46199</c:v>
+                </c:pt>
+                <c:pt idx="2276">
+                  <c:v>46202</c:v>
+                </c:pt>
               </c:numCache>
             </c:numRef>
           </c:cat>
@@ -13950,6 +13956,12 @@
                 </c:pt>
                 <c:pt idx="2274">
                   <c:v>157000</c:v>
+                </c:pt>
+                <c:pt idx="2275">
+                  <c:v>152500</c:v>
+                </c:pt>
+                <c:pt idx="2276">
+                  <c:v>151750</c:v>
                 </c:pt>
               </c:numCache>
             </c:numRef>
@@ -15029,7 +15041,7 @@
 
 <file path=xl/worksheets/sheet1.xml><?xml version="1.0" encoding="utf-8"?>
 <worksheet xmlns="http://schemas.openxmlformats.org/spreadsheetml/2006/main" xmlns:r="http://schemas.openxmlformats.org/officeDocument/2006/relationships" xmlns:mc="http://schemas.openxmlformats.org/markup-compatibility/2006" xmlns:x14ac="http://schemas.microsoft.com/office/spreadsheetml/2009/9/ac" xmlns:xr="http://schemas.microsoft.com/office/spreadsheetml/2014/revision" xmlns:xr2="http://schemas.microsoft.com/office/spreadsheetml/2015/revision2" xmlns:xr3="http://schemas.microsoft.com/office/spreadsheetml/2016/revision3" mc:Ignorable="x14ac xr xr2 xr3" xr:uid="{00000000-0001-0000-0000-000000000000}">
-  <dimension ref="A1:H2276"/>
+  <dimension ref="A1:H2278"/>
   <sheetFormatPr defaultColWidth="9" defaultRowHeight="14.4"/>
   <cols>
     <col min="1" max="1" width="10.77734375" style="16" bestFit="1" customWidth="1"/>
@@ -61524,6 +61536,58 @@
       </c>
       <c r="H2276" s="15">
         <v>157000</v>
+      </c>
+    </row>
+    <row r="2277" spans="1:8">
+      <c r="A2277" s="16">
+        <v>46199</v>
+      </c>
+      <c r="B2277" s="16">
+        <v>46199</v>
+      </c>
+      <c r="C2277" s="10">
+        <v>0.625</v>
+      </c>
+      <c r="D2277" s="9" t="s">
+        <v>10</v>
+      </c>
+      <c r="E2277" s="17">
+        <v>152500</v>
+      </c>
+      <c r="F2277" s="17">
+        <v>158000</v>
+      </c>
+      <c r="G2277" s="17">
+        <v>147000</v>
+      </c>
+      <c r="H2277" s="15">
+        <v>152500</v>
+      </c>
+    </row>
+    <row r="2278" spans="1:8">
+      <c r="A2278" s="16">
+        <v>46202</v>
+      </c>
+      <c r="B2278" s="14">
+        <v>46202</v>
+      </c>
+      <c r="C2278" s="10">
+        <v>0.625</v>
+      </c>
+      <c r="D2278" s="9" t="s">
+        <v>10</v>
+      </c>
+      <c r="E2278" s="17">
+        <v>151750</v>
+      </c>
+      <c r="F2278" s="17">
+        <v>158000</v>
+      </c>
+      <c r="G2278" s="17">
+        <v>145500</v>
+      </c>
+      <c r="H2278" s="15">
+        <v>151750</v>
       </c>
     </row>
   </sheetData>

--- a/data/commodity/Lithium.xlsx
+++ b/data/commodity/Lithium.xlsx
@@ -1,16 +1,16 @@
 
 <file path=xl/workbook.xml><?xml version="1.0" encoding="utf-8"?>
 <workbook xmlns="http://schemas.openxmlformats.org/spreadsheetml/2006/main" xmlns:r="http://schemas.openxmlformats.org/officeDocument/2006/relationships" xmlns:mc="http://schemas.openxmlformats.org/markup-compatibility/2006" xmlns:x15="http://schemas.microsoft.com/office/spreadsheetml/2010/11/main" xmlns:xr="http://schemas.microsoft.com/office/spreadsheetml/2014/revision" xmlns:xr6="http://schemas.microsoft.com/office/spreadsheetml/2016/revision6" xmlns:xr10="http://schemas.microsoft.com/office/spreadsheetml/2016/revision10" xmlns:xr2="http://schemas.microsoft.com/office/spreadsheetml/2015/revision2" mc:Ignorable="x15 xr xr6 xr10 xr2">
-  <fileVersion appName="xl" lastEdited="7" lowestEdited="6" rupBuild="30026"/>
+  <fileVersion appName="xl" lastEdited="7" lowestEdited="6" rupBuild="30131"/>
   <workbookPr/>
   <mc:AlternateContent xmlns:mc="http://schemas.openxmlformats.org/markup-compatibility/2006">
     <mc:Choice Requires="x15">
-      <x15ac:absPath xmlns:x15ac="http://schemas.microsoft.com/office/spreadsheetml/2010/11/ac" url="C:\Users\krm\PycharmProjects\AlternativeData\data\commodity\"/>
+      <x15ac:absPath xmlns:x15ac="http://schemas.microsoft.com/office/spreadsheetml/2010/11/ac" url="C:\Users\Geust\PycharmProjects\AlternativeData\data\commodity\"/>
     </mc:Choice>
   </mc:AlternateContent>
-  <xr:revisionPtr revIDLastSave="0" documentId="13_ncr:1_{BA2A05DB-CBC6-4276-92D2-B664D84FC248}" xr6:coauthVersionLast="47" xr6:coauthVersionMax="47" xr10:uidLastSave="{00000000-0000-0000-0000-000000000000}"/>
+  <xr:revisionPtr revIDLastSave="0" documentId="13_ncr:1_{29D20D7C-69D9-47FA-8BD9-329E78963B28}" xr6:coauthVersionLast="47" xr6:coauthVersionMax="47" xr10:uidLastSave="{00000000-0000-0000-0000-000000000000}"/>
   <bookViews>
-    <workbookView xWindow="28680" yWindow="-120" windowWidth="29040" windowHeight="15720" xr2:uid="{00000000-000D-0000-FFFF-FFFF00000000}"/>
+    <workbookView xWindow="20" yWindow="20" windowWidth="23020" windowHeight="14620" xr2:uid="{00000000-000D-0000-FFFF-FFFF00000000}"/>
   </bookViews>
   <sheets>
     <sheet name="Lithium" sheetId="1" r:id="rId1"/>
@@ -36,7 +36,7 @@
 </file>
 
 <file path=xl/sharedStrings.xml><?xml version="1.0" encoding="utf-8"?>
-<sst xmlns="http://schemas.openxmlformats.org/spreadsheetml/2006/main" count="2291" uniqueCount="16">
+<sst xmlns="http://schemas.openxmlformats.org/spreadsheetml/2006/main" count="2293" uniqueCount="16">
   <si>
     <t>source</t>
     <phoneticPr fontId="2" type="noConversion"/>
@@ -231,9 +231,9 @@
     </xf>
   </cellXfs>
   <cellStyles count="3">
-    <cellStyle name="쉼표" xfId="1" builtinId="3"/>
-    <cellStyle name="표준" xfId="0" builtinId="0"/>
-    <cellStyle name="하이퍼링크" xfId="2" builtinId="8"/>
+    <cellStyle name="Comma" xfId="1" builtinId="3"/>
+    <cellStyle name="Hyperlink" xfId="2" builtinId="8"/>
+    <cellStyle name="Normal" xfId="0" builtinId="0"/>
   </cellStyles>
   <dxfs count="0"/>
   <tableStyles count="0" defaultTableStyle="TableStyleMedium2" defaultPivotStyle="PivotStyleLight16"/>
@@ -251,7 +251,7 @@
 <file path=xl/charts/chart1.xml><?xml version="1.0" encoding="utf-8"?>
 <c:chartSpace xmlns:c="http://schemas.openxmlformats.org/drawingml/2006/chart" xmlns:a="http://schemas.openxmlformats.org/drawingml/2006/main" xmlns:r="http://schemas.openxmlformats.org/officeDocument/2006/relationships" xmlns:c16r2="http://schemas.microsoft.com/office/drawing/2015/06/chart">
   <c:date1904 val="0"/>
-  <c:lang val="ko-KR"/>
+  <c:lang val="en-US"/>
   <c:roundedCorners val="0"/>
   <mc:AlternateContent xmlns:mc="http://schemas.openxmlformats.org/markup-compatibility/2006">
     <mc:Choice xmlns:c14="http://schemas.microsoft.com/office/drawing/2007/8/2/chart" Requires="c14">
@@ -7123,6 +7123,12 @@
                 <c:pt idx="2276">
                   <c:v>46202</c:v>
                 </c:pt>
+                <c:pt idx="2277">
+                  <c:v>46203</c:v>
+                </c:pt>
+                <c:pt idx="2278">
+                  <c:v>46204</c:v>
+                </c:pt>
               </c:numCache>
             </c:numRef>
           </c:cat>
@@ -13962,6 +13968,12 @@
                 </c:pt>
                 <c:pt idx="2276">
                   <c:v>151750</c:v>
+                </c:pt>
+                <c:pt idx="2277">
+                  <c:v>156500</c:v>
+                </c:pt>
+                <c:pt idx="2278">
+                  <c:v>160000</c:v>
                 </c:pt>
               </c:numCache>
             </c:numRef>
@@ -15041,15 +15053,15 @@
 
 <file path=xl/worksheets/sheet1.xml><?xml version="1.0" encoding="utf-8"?>
 <worksheet xmlns="http://schemas.openxmlformats.org/spreadsheetml/2006/main" xmlns:r="http://schemas.openxmlformats.org/officeDocument/2006/relationships" xmlns:mc="http://schemas.openxmlformats.org/markup-compatibility/2006" xmlns:x14ac="http://schemas.microsoft.com/office/spreadsheetml/2009/9/ac" xmlns:xr="http://schemas.microsoft.com/office/spreadsheetml/2014/revision" xmlns:xr2="http://schemas.microsoft.com/office/spreadsheetml/2015/revision2" xmlns:xr3="http://schemas.microsoft.com/office/spreadsheetml/2016/revision3" mc:Ignorable="x14ac xr xr2 xr3" xr:uid="{00000000-0001-0000-0000-000000000000}">
-  <dimension ref="A1:H2278"/>
-  <sheetFormatPr defaultColWidth="9" defaultRowHeight="14.4"/>
+  <dimension ref="A1:H2280"/>
+  <sheetFormatPr defaultColWidth="9" defaultRowHeight="14.5"/>
   <cols>
-    <col min="1" max="1" width="10.77734375" style="16" bestFit="1" customWidth="1"/>
-    <col min="2" max="2" width="12.109375" style="14" bestFit="1" customWidth="1"/>
-    <col min="3" max="3" width="10.6640625" style="18" bestFit="1" customWidth="1"/>
-    <col min="4" max="4" width="10" style="19" bestFit="1" customWidth="1"/>
-    <col min="5" max="7" width="11.44140625" style="17" customWidth="1"/>
-    <col min="8" max="8" width="10.77734375" style="15" bestFit="1" customWidth="1"/>
+    <col min="1" max="1" width="10.08984375" style="16" bestFit="1" customWidth="1"/>
+    <col min="2" max="2" width="11.6328125" style="14" bestFit="1" customWidth="1"/>
+    <col min="3" max="3" width="10.08984375" style="18" bestFit="1" customWidth="1"/>
+    <col min="4" max="4" width="9.54296875" style="19" bestFit="1" customWidth="1"/>
+    <col min="5" max="7" width="8.54296875" style="17" bestFit="1" customWidth="1"/>
+    <col min="8" max="8" width="8.54296875" style="15" bestFit="1" customWidth="1"/>
   </cols>
   <sheetData>
     <row r="1" spans="1:8" s="8" customFormat="1">
@@ -61588,6 +61600,58 @@
       </c>
       <c r="H2278" s="15">
         <v>151750</v>
+      </c>
+    </row>
+    <row r="2279" spans="1:8">
+      <c r="A2279" s="16">
+        <v>46203</v>
+      </c>
+      <c r="B2279" s="16">
+        <v>46203</v>
+      </c>
+      <c r="C2279" s="10">
+        <v>0.625</v>
+      </c>
+      <c r="D2279" s="9" t="s">
+        <v>10</v>
+      </c>
+      <c r="E2279" s="17">
+        <v>156500</v>
+      </c>
+      <c r="F2279" s="17">
+        <v>162000</v>
+      </c>
+      <c r="G2279" s="17">
+        <v>151000</v>
+      </c>
+      <c r="H2279" s="15">
+        <v>156500</v>
+      </c>
+    </row>
+    <row r="2280" spans="1:8">
+      <c r="A2280" s="16">
+        <v>46204</v>
+      </c>
+      <c r="B2280" s="14">
+        <v>46204</v>
+      </c>
+      <c r="C2280" s="10">
+        <v>0.625</v>
+      </c>
+      <c r="D2280" s="9" t="s">
+        <v>10</v>
+      </c>
+      <c r="E2280" s="17">
+        <v>156531</v>
+      </c>
+      <c r="F2280" s="17">
+        <v>165000</v>
+      </c>
+      <c r="G2280" s="17">
+        <v>155000</v>
+      </c>
+      <c r="H2280" s="15">
+        <v>160000</v>
       </c>
     </row>
   </sheetData>
@@ -61600,9 +61664,9 @@
 <file path=xl/worksheets/sheet2.xml><?xml version="1.0" encoding="utf-8"?>
 <worksheet xmlns="http://schemas.openxmlformats.org/spreadsheetml/2006/main" xmlns:r="http://schemas.openxmlformats.org/officeDocument/2006/relationships" xmlns:mc="http://schemas.openxmlformats.org/markup-compatibility/2006" xmlns:x14ac="http://schemas.microsoft.com/office/spreadsheetml/2009/9/ac" xmlns:xr="http://schemas.microsoft.com/office/spreadsheetml/2014/revision" xmlns:xr2="http://schemas.microsoft.com/office/spreadsheetml/2015/revision2" xmlns:xr3="http://schemas.microsoft.com/office/spreadsheetml/2016/revision3" mc:Ignorable="x14ac xr xr2 xr3" xr:uid="{9FF8FA39-E640-4E6A-B261-45B6002B9973}">
   <dimension ref="B2:C4"/>
-  <sheetFormatPr defaultColWidth="8.77734375" defaultRowHeight="14.4"/>
+  <sheetFormatPr defaultColWidth="8.81640625" defaultRowHeight="14.5"/>
   <cols>
-    <col min="2" max="2" width="10.44140625" bestFit="1" customWidth="1"/>
+    <col min="2" max="2" width="10.453125" bestFit="1" customWidth="1"/>
   </cols>
   <sheetData>
     <row r="2" spans="2:3">
@@ -61642,7 +61706,7 @@
 <file path=xl/worksheets/sheet3.xml><?xml version="1.0" encoding="utf-8"?>
 <worksheet xmlns="http://schemas.openxmlformats.org/spreadsheetml/2006/main" xmlns:r="http://schemas.openxmlformats.org/officeDocument/2006/relationships" xmlns:mc="http://schemas.openxmlformats.org/markup-compatibility/2006" xmlns:x14ac="http://schemas.microsoft.com/office/spreadsheetml/2009/9/ac" xmlns:xr="http://schemas.microsoft.com/office/spreadsheetml/2014/revision" xmlns:xr2="http://schemas.microsoft.com/office/spreadsheetml/2015/revision2" xmlns:xr3="http://schemas.microsoft.com/office/spreadsheetml/2016/revision3" mc:Ignorable="x14ac xr xr2 xr3" xr:uid="{17A1C1D3-27CA-4F31-B658-DBB84930A46D}">
   <dimension ref="A1"/>
-  <sheetFormatPr defaultColWidth="8.77734375" defaultRowHeight="14.4"/>
+  <sheetFormatPr defaultColWidth="8.81640625" defaultRowHeight="14.5"/>
   <sheetData/>
   <phoneticPr fontId="2" type="noConversion"/>
   <pageMargins left="0.7" right="0.7" top="0.75" bottom="0.75" header="0.3" footer="0.3"/>
